--- a/projects/mihomes/MHO_model.xlsx
+++ b/projects/mihomes/MHO_model.xlsx
@@ -657,7 +657,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Three-statement model, DCF and comparable companies analysis. Built 04-Sep-2026.</t>
+          <t>Three-statement model, DCF and comparable companies analysis. Built 04-Sep-2026; market data refreshed 11-Sep-2026.</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
+    <row r="19" ht="48" customHeight="1">
       <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Rates</t>
@@ -818,11 +818,11 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>FRED. 30-yr fixed mortgage (MORTGAGE30US) 6.71% at 03-Sep-2026; 10-yr UST (DGS10) 4.79%; BB high-yield effective yield (BAMLH0A1HYBBEY) 6.03%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
+          <t>FRED, pulled 11-Sep-2026. 30-yr fixed mortgage (MORTGAGE30US) 6.76% at 2026-09-10, up from a 5.98% trough this year; 2026 year-to-date average 6.38%. 10-yr UST (DGS10) 4.95%, 30-yr 5.37%. Annual mortgage figures are calendar-year averages of the weekly series, recomputed rather than typed — they had been lagged a year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Housing macro</t>
@@ -830,7 +830,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>FRED. Raleigh house price index (ATNHPIUS39580Q) 365.5 → 367.2 over the year to Q2-2026, +0.4%. Charlotte (ATNHPIUS16740Q) +1.1%. NC private building permits (NCBPPRIVSA) declining through 2026.</t>
+          <t>FRED, pulled 11-Sep-2026. Raleigh house price index (ATNHPIUS39580Q) +1.1% and Charlotte (ATNHPIUS16740Q) +1.5% over the year to Q2 2026, against 3.8% CPI — -2.6% and -2.3% in real terms. The FHFA All-Transactions index is NOT seasonally adjusted, so changes are measured year-over-year; a three-quarter window understates growth by about a point. NC private building permits (NCBPPRIVSA) declining through 2026.</t>
         </is>
       </c>
     </row>
@@ -911,11 +911,11 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Of the $2.12 of 2027E EPS growth over 2026E: $1.08 is volume, price, cost and buyback; $0.40 is the mortgage-rate decline; $0.63 — 30% — is the Southern competition premium decaying. The rate path and the premium together, 49% of the step-up, are Tier 3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="48" customHeight="1">
+          <t>Of the $1.17 of 2027E EPS growth over 2026E: $0.90 is volume, price, cost and buyback; $-0.36 is the mortgage-rate decline; $0.64 — 55% — is the Southern competition premium decaying. The rate path and the premium together, 24% of the step-up, are Tier 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="72" customHeight="1">
       <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Versus consensus</t>
@@ -923,7 +923,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Four analysts cover MHO. My 2026E EPS of $11.94 and 2027E of $14.06 both sit below the lowest published estimate (2026 range $11.96–$13.34, 2027 range $14.24–$16.49). Consensus target $170.67 against mine of $150, rating Buy against mine of Underweight. The gap is the Southern margin recovery, which I do not underwrite as fully as the street does.</t>
+          <t>Coverage is thin and stale. 7 analysts have rated MHO in the past twelve months (4 positive, 2 hold, 1 sell; most recent action: Zacks Research downgrade on 9 September 2026), consensus target $164.25 against mine of $160. But only ONE price target has been issued in the past three months, and the EPS estimates below are stamped 2026-06-24: 2026E $12.19 (range $11.43-$13.25), 2027E $14.08 (no range published). Mine are $11.98 and $13.15 — below on both years, but 2026 sits INSIDE the published range, not under it. Sources: marketbeat.com for ratings and target, stockanalysis.com for EPS; see data/consensus.json.</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Roughly 74%. That is unavoidable for a cyclical with heavy near-term working capital investment. The DCF still carries 60% of the target, because the alternative — the peer multiple — prices a re-rating the company has not earned.</t>
+          <t>Roughly 78%. That is unavoidable for a cyclical with heavy near-term working capital investment. The DCF still carries 60% of the target, because the alternative — the peer multiple — prices a re-rating the company has not earned.</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Q37"/>
+  <dimension ref="B2:Q36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.2" customWidth="1" min="1" max="1"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="C6" s="40" t="n">
-        <v>142.94</v>
+        <v>137.89</v>
       </c>
       <c r="D6" s="41" t="n">
-        <v>39980</v>
+        <v>38570</v>
       </c>
       <c r="E6" s="41" t="n">
         <v>23820</v>
@@ -1247,7 +1247,7 @@
         <v>164</v>
       </c>
       <c r="G6" s="73" t="n">
-        <v>13.6</v>
+        <v>13.12</v>
       </c>
       <c r="H6" s="41" t="n">
         <v>33350</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="C7" s="40" t="n">
-        <v>83.88</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D7" s="41" t="n">
-        <v>20210</v>
+        <v>19180</v>
       </c>
       <c r="E7" s="41" t="n">
         <v>21621</v>
@@ -1304,7 +1304,7 @@
         <v>3632</v>
       </c>
       <c r="G7" s="73" t="n">
-        <v>13.12</v>
+        <v>12.37</v>
       </c>
       <c r="H7" s="41" t="n">
         <v>32740</v>
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>124.36</v>
+        <v>117.85</v>
       </c>
       <c r="D8" s="41" t="n">
-        <v>23310</v>
+        <v>22170</v>
       </c>
       <c r="E8" s="41" t="n">
         <v>13014</v>
@@ -1361,7 +1361,7 @@
         <v>86</v>
       </c>
       <c r="G8" s="73" t="n">
-        <v>12.68</v>
+        <v>12.06</v>
       </c>
       <c r="H8" s="41" t="n">
         <v>16410</v>
@@ -1406,10 +1406,10 @@
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>141.43</v>
+        <v>134.92</v>
       </c>
       <c r="D9" s="41" t="n">
-        <v>13030</v>
+        <v>12430</v>
       </c>
       <c r="E9" s="41" t="n">
         <v>8531</v>
@@ -1418,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="73" t="n">
-        <v>11.32</v>
+        <v>10.81</v>
       </c>
       <c r="H9" s="41" t="n">
         <v>10760</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>67.75</v>
+        <v>64.22</v>
       </c>
       <c r="D10" s="41" t="n">
-        <v>4420</v>
+        <v>4190</v>
       </c>
       <c r="E10" s="41" t="n">
         <v>5058</v>
@@ -1475,7 +1475,7 @@
         <v>34</v>
       </c>
       <c r="G10" s="73" t="n">
-        <v>14.07</v>
+        <v>13.39</v>
       </c>
       <c r="H10" s="41" t="n">
         <v>5390</v>
@@ -1514,428 +1514,396 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="72" t="inlineStr">
-        <is>
-          <t>TPH — Tri Pointe</t>
-        </is>
-      </c>
-      <c r="C11" s="40" t="n">
-        <v>46.95</v>
-      </c>
-      <c r="D11" s="41" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E11" s="41" t="n">
-        <v>3141</v>
-      </c>
-      <c r="F11" s="41" t="n">
-        <v>156</v>
-      </c>
-      <c r="G11" s="73" t="n">
-        <v>22.24</v>
-      </c>
-      <c r="H11" s="41" t="n">
-        <v>3250</v>
-      </c>
-      <c r="I11" s="13">
-        <f>D11/G11</f>
-        <v/>
-      </c>
-      <c r="J11" s="48">
-        <f>D11/C11</f>
-        <v/>
-      </c>
-      <c r="K11" s="50">
-        <f>E11/J11</f>
-        <v/>
-      </c>
-      <c r="L11" s="50">
-        <f>(E11-F11)/J11</f>
-        <v/>
-      </c>
-      <c r="M11" s="60">
-        <f>C11/K11</f>
-        <v/>
-      </c>
-      <c r="N11" s="60">
-        <f>C11/L11</f>
-        <v/>
-      </c>
-      <c r="O11" s="16">
-        <f>I11/E11</f>
-        <v/>
-      </c>
-      <c r="P11" s="74">
-        <f>G11*O11</f>
-        <v/>
-      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Peer median</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="75">
+        <f>MEDIAN(G6:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="19" t="n"/>
+      <c r="M11" s="75">
+        <f>MEDIAN(M6:M10)</f>
+        <v/>
+      </c>
+      <c r="N11" s="75">
+        <f>MEDIAN(N6:N10)</f>
+        <v/>
+      </c>
+      <c r="O11" s="76">
+        <f>MEDIAN(O6:O10)</f>
+        <v/>
+      </c>
+      <c r="P11" s="19" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>Peer median</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="n"/>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="19" t="n"/>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="75">
-        <f>MEDIAN(G6:G11)</f>
-        <v/>
-      </c>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="75">
-        <f>MEDIAN(M6:M11)</f>
-        <v/>
-      </c>
-      <c r="N12" s="75">
-        <f>MEDIAN(N6:N11)</f>
-        <v/>
-      </c>
-      <c r="O12" s="76">
-        <f>MEDIAN(O6:O11)</f>
-        <v/>
-      </c>
-      <c r="P12" s="19" t="n"/>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Peer mean</t>
+        </is>
+      </c>
+      <c r="G12" s="77">
+        <f>AVERAGE(G6:G10)</f>
+        <v/>
+      </c>
+      <c r="M12" s="77">
+        <f>AVERAGE(M6:M10)</f>
+        <v/>
+      </c>
+      <c r="N12" s="77">
+        <f>AVERAGE(N6:N10)</f>
+        <v/>
+      </c>
+      <c r="O12" s="34">
+        <f>AVERAGE(O6:O10)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Peer mean</t>
-        </is>
-      </c>
-      <c r="G13" s="77">
-        <f>AVERAGE(G6:G11)</f>
-        <v/>
-      </c>
-      <c r="M13" s="77">
-        <f>AVERAGE(M6:M11)</f>
-        <v/>
-      </c>
-      <c r="N13" s="77">
-        <f>AVERAGE(N6:N11)</f>
-        <v/>
-      </c>
-      <c r="O13" s="34">
-        <f>AVERAGE(O6:O11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>MHO — M/I Homes</t>
         </is>
       </c>
-      <c r="C14" s="78" t="n">
-        <v>148.26</v>
-      </c>
-      <c r="D14" s="79" t="n">
-        <v>3748</v>
-      </c>
-      <c r="E14" s="79" t="n">
+      <c r="C13" s="78" t="n">
+        <v>140.07</v>
+      </c>
+      <c r="D13" s="79" t="n">
+        <v>3540</v>
+      </c>
+      <c r="E13" s="79" t="n">
         <v>3227</v>
       </c>
-      <c r="F14" s="79" t="n">
+      <c r="F13" s="79" t="n">
         <v>16</v>
       </c>
-      <c r="G14" s="80" t="n">
-        <v>12.41</v>
-      </c>
-      <c r="H14" s="79" t="n">
+      <c r="G13" s="80" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="H13" s="79" t="n">
         <v>4260</v>
       </c>
-      <c r="I14" s="64">
-        <f>D14/G14</f>
-        <v/>
-      </c>
-      <c r="J14" s="81">
-        <f>D14/C14</f>
-        <v/>
-      </c>
-      <c r="K14" s="82">
-        <f>E14/J14</f>
-        <v/>
-      </c>
-      <c r="L14" s="82">
-        <f>(E14-F14)/J14</f>
-        <v/>
-      </c>
-      <c r="M14" s="83">
-        <f>C14/K14</f>
-        <v/>
-      </c>
-      <c r="N14" s="83">
-        <f>C14/L14</f>
-        <v/>
-      </c>
-      <c r="O14" s="12">
-        <f>I14/E14</f>
-        <v/>
-      </c>
-      <c r="P14" s="83">
-        <f>G14*O14</f>
-        <v/>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
+      <c r="I13" s="64">
+        <f>D13/G13</f>
+        <v/>
+      </c>
+      <c r="J13" s="81">
+        <f>D13/C13</f>
+        <v/>
+      </c>
+      <c r="K13" s="82">
+        <f>E13/J13</f>
+        <v/>
+      </c>
+      <c r="L13" s="82">
+        <f>(E13-F13)/J13</f>
+        <v/>
+      </c>
+      <c r="M13" s="83">
+        <f>C13/K13</f>
+        <v/>
+      </c>
+      <c r="N13" s="83">
+        <f>C13/L13</f>
+        <v/>
+      </c>
+      <c r="O13" s="12">
+        <f>I13/E13</f>
+        <v/>
+      </c>
+      <c r="P13" s="83">
+        <f>G13*O13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="9" t="inlineStr">
         <is>
           <t>MHO screens ~17% below the peer median on P/B — but it also earns a lower return on that book than any peer except the two trading below book.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15.5" customHeight="1">
-      <c r="B16" s="3" t="inlineStr">
+    <row r="15" ht="15.5" customHeight="1">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>WHAT THE COMP SET ACTUALLY SHOWS</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
-      <c r="P16" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>P/B = (MktCap/NI) x (NI/Equity) = P/E x ROE. That is an accounting identity, not an empirical result — the P/E x ROE column above reproduces P/B exactly for every company.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>P/B = (MktCap/NI) x (NI/Equity) = P/E x ROE. That is an accounting identity, not an empirical result — the P/E x ROE column above reproduces P/B exactly for every company.</t>
+          <t>So there is no independent information in a fitted line through P/B and ROE, and none is attempted here. The observation that survives is about DISPERSION: peer earnings</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>So there is no independent information in a fitted line through P/B and ROE, and none is attempted here. The observation that survives is about DISPERSION: peer earnings</t>
+          <t>multiples sit in a narrow band while returns on equity do not. The market is paying similar earnings multiples for very different returns on capital.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>multiples sit in a narrow band while returns on equity do not. The market is paying similar earnings multiples for very different returns on capital.</t>
+          <t>The practical consequence: P/B and P/E are ONE view of this stock, not two, so they are counted once. And because the multiple barely moves with the return, MHO's</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>The practical consequence: P/B and P/E are ONE view of this stock, not two, so they are counted once. And because the multiple barely moves with the return, MHO's</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="10" t="inlineStr">
-        <is>
           <t>depressed ROE shows up in the earnings rather than in the multiple — which is why the peer-based valuation below simply applies the peer median P/E to our own EPS estimate.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="15.5" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="15.5" customHeight="1">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>DISPERSION — peer earnings multiples vs peer returns (Tri Pointe shown but excluded: its 22x P/E reflects trough earnings)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
-      <c r="P23" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n"/>
+      <c r="P22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Peer P/E — low</t>
+        </is>
+      </c>
+      <c r="E23" s="60">
+        <f>MIN(G6:G10)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Peer P/E — low</t>
+          <t>Peer P/E — high</t>
         </is>
       </c>
       <c r="E24" s="60">
-        <f>MIN(G6:G10)</f>
+        <f>MAX(G6:G10)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Peer P/E — high</t>
-        </is>
-      </c>
-      <c r="E25" s="60">
-        <f>MAX(G6:G10)</f>
-        <v/>
+          <t>Peer P/E — coefficient of variation</t>
+        </is>
+      </c>
+      <c r="E25" s="16">
+        <f>STDEVP(G6:G10)/AVERAGE(G6:G10)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="9" t="inlineStr">
+        <is>
+          <t>Earnings multiples are tightly clustered.</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Peer P/E — coefficient of variation</t>
+          <t>Peer ROE — low</t>
         </is>
       </c>
       <c r="E26" s="16">
-        <f>STDEVP(G6:G10)/AVERAGE(G6:G10)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="9" t="inlineStr">
-        <is>
-          <t>Earnings multiples are tightly clustered.</t>
-        </is>
+        <f>MIN(O6:O10)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Peer ROE — low</t>
+          <t>Peer ROE — high</t>
         </is>
       </c>
       <c r="E27" s="16">
-        <f>MIN(O6:O10)</f>
+        <f>MAX(O6:O10)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Peer ROE — high</t>
-        </is>
-      </c>
-      <c r="E28" s="16">
-        <f>MAX(O6:O10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Peer ROE — coefficient of variation</t>
         </is>
       </c>
-      <c r="E29" s="12">
+      <c r="E28" s="12">
         <f>STDEVP(O6:O10)/AVERAGE(O6:O10)</f>
         <v/>
       </c>
-      <c r="Q29" s="9" t="inlineStr">
+      <c r="Q28" s="9" t="inlineStr">
         <is>
           <t>Returns vary roughly four times as much as the multiples that price them.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31">
-      <c r="B31" s="10" t="inlineStr">
+    <row r="29" ht="6" customHeight="1"/>
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Normalised ROE implied by the current share price</t>
         </is>
       </c>
-      <c r="E31" s="84">
-        <f>3.5+M14*(DCF!$C$9-3.5)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="9" t="inlineStr">
+      <c r="E30" s="84">
+        <f>3.5+M13*(DCF!$C$9-3.5)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="9" t="inlineStr">
         <is>
           <t>At an 11.5% cost of equity and 3.5% long-run growth, a 1.16x book multiple already pays for a normalised return on equity of roughly 12.8%. The base case reaches 12.2% by 2029, so the recovery is largely in the price.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="6" customHeight="1"/>
-    <row r="33" ht="15.5" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="31" ht="6" customHeight="1"/>
+    <row r="32" ht="15.5" customHeight="1">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>IMPLIED VALUE PER SHARE</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
-      <c r="P33" s="3" t="n"/>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n"/>
+      <c r="N32" s="3" t="n"/>
+      <c r="O32" s="3" t="n"/>
+      <c r="P32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Applied to</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>Value $</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>Applied to</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="inlineStr">
-        <is>
-          <t>Value $</t>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Peer median P/B on Sep-2027E book</t>
+        </is>
+      </c>
+      <c r="C34" s="60">
+        <f>M11</f>
+        <v/>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Book value at Sep-2027 (est.)</t>
+        </is>
+      </c>
+      <c r="H34" s="85">
+        <f>C34*((BS!F25)+(BS!G25))/2</f>
+        <v/>
+      </c>
+      <c r="Q34" s="9" t="inlineStr">
+        <is>
+          <t>THE comparables method. The median multiple the comp set trades at, applied to our own book estimate. Scenarios instead take the multiple the market puts on the builder actually earning that return — Meritage for the bear case, Toll Brothers for the bull — so every multiple in the model belongs to a company you can look up.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Peer median P/B on Sep-2027E book</t>
+          <t>Memo: peer median P/E on 2027E EPS</t>
         </is>
       </c>
       <c r="C35" s="60">
-        <f>M12</f>
+        <f>G11</f>
         <v/>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Book value at Sep-2027 (est.)</t>
+          <t>2027E diluted EPS</t>
         </is>
       </c>
       <c r="H35" s="85">
-        <f>C35*((BS!F25)+(BS!G25))/2</f>
+        <f>C35*IS!G37</f>
         <v/>
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>THE comparables method. The median multiple the comp set trades at, applied to our own book estimate. Scenarios instead take the multiple the market puts on the builder actually earning that return — Meritage for the bear case, Toll Brothers for the bull — so every multiple in the model belongs to a company you can look up.</t>
+          <t>Cross-check only, NOT weighted. The identity P/B = P/E x ROE means this is the same view restated.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Memo: peer median P/E on 2027E EPS</t>
+          <t>Memo: MHO's own P/E on 2027E EPS</t>
         </is>
       </c>
       <c r="C36" s="60">
-        <f>G12</f>
+        <f>G13</f>
         <v/>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1948,31 +1916,6 @@
         <v/>
       </c>
       <c r="Q36" s="9" t="inlineStr">
-        <is>
-          <t>Cross-check only, NOT weighted. The identity P/B = P/E x ROE means this is the same view restated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Memo: MHO's own P/E on 2027E EPS</t>
-        </is>
-      </c>
-      <c r="C37" s="60">
-        <f>G14</f>
-        <v/>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>2027E diluted EPS</t>
-        </is>
-      </c>
-      <c r="H37" s="85">
-        <f>C37*IS!G37</f>
-        <v/>
-      </c>
-      <c r="Q37" s="9" t="inlineStr">
         <is>
           <t>NOT a valuation. This reduces algebraically to today's share price scaled by our own EPS growth, so it cannot disagree with the market. Shown only to document why it is not used.</t>
         </is>
@@ -2109,7 +2052,7 @@
         </is>
       </c>
       <c r="C12" s="51">
-        <f>Assumptions!G28</f>
+        <f>Assumptions!G30</f>
         <v/>
       </c>
     </row>
@@ -2142,7 +2085,7 @@
         </is>
       </c>
       <c r="C15" s="86">
-        <f>Assumptions!G14</f>
+        <f>Assumptions!G16</f>
         <v/>
       </c>
     </row>
@@ -2164,7 +2107,7 @@
         </is>
       </c>
       <c r="C17" s="86">
-        <f>Assumptions!$C$12</f>
+        <f>Assumptions!$C$14</f>
         <v/>
       </c>
     </row>
@@ -2175,7 +2118,7 @@
         </is>
       </c>
       <c r="C18" s="87">
-        <f>Assumptions!$C$13</f>
+        <f>Assumptions!$C$15</f>
         <v/>
       </c>
     </row>
@@ -2186,7 +2129,7 @@
         </is>
       </c>
       <c r="C19" s="86">
-        <f>Assumptions!$C$15</f>
+        <f>Assumptions!$C$17</f>
         <v/>
       </c>
     </row>
@@ -2197,7 +2140,7 @@
         </is>
       </c>
       <c r="C20" s="87">
-        <f>Assumptions!$C$16</f>
+        <f>Assumptions!$C$18</f>
         <v/>
       </c>
     </row>
@@ -2208,7 +2151,7 @@
         </is>
       </c>
       <c r="C21" s="86">
-        <f>Assumptions!G30</f>
+        <f>Assumptions!G32</f>
         <v/>
       </c>
     </row>
@@ -2219,7 +2162,7 @@
         </is>
       </c>
       <c r="C22" s="86">
-        <f>Assumptions!G31</f>
+        <f>Assumptions!G33</f>
         <v/>
       </c>
     </row>
@@ -2230,7 +2173,7 @@
         </is>
       </c>
       <c r="C23" s="86">
-        <f>Assumptions!$C$37</f>
+        <f>Assumptions!$C$39</f>
         <v/>
       </c>
     </row>
@@ -2241,7 +2184,7 @@
         </is>
       </c>
       <c r="C24" s="51">
-        <f>Assumptions!G32</f>
+        <f>Assumptions!G34</f>
         <v/>
       </c>
     </row>
@@ -2252,7 +2195,7 @@
         </is>
       </c>
       <c r="C25" s="51">
-        <f>Assumptions!G33</f>
+        <f>Assumptions!G35</f>
         <v/>
       </c>
     </row>
@@ -2263,7 +2206,7 @@
         </is>
       </c>
       <c r="C26" s="51">
-        <f>Assumptions!G34</f>
+        <f>Assumptions!G36</f>
         <v/>
       </c>
     </row>
@@ -2274,7 +2217,7 @@
         </is>
       </c>
       <c r="C27" s="86">
-        <f>Assumptions!$C$38</f>
+        <f>Assumptions!$C$40</f>
         <v/>
       </c>
     </row>
@@ -2285,7 +2228,7 @@
         </is>
       </c>
       <c r="C28" s="86">
-        <f>Assumptions!$C$35</f>
+        <f>Assumptions!$C$37</f>
         <v/>
       </c>
     </row>
@@ -2296,7 +2239,7 @@
         </is>
       </c>
       <c r="C29" s="88">
-        <f>Assumptions!$C$36</f>
+        <f>Assumptions!$C$38</f>
         <v/>
       </c>
     </row>
@@ -2691,7 +2634,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Prepared 04-Sep-2026.  All figures traceable to SEC filings; see README for sources.</t>
+          <t>Prepared 04-Sep-2026; market data refreshed 11-Sep-2026.  All figures traceable to SEC filings; see README for sources.</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2661,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>UNDERWEIGHT</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2672,7 @@
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
@@ -2744,7 +2687,7 @@
         </is>
       </c>
       <c r="C8" s="11">
-        <f>Assumptions!$C$60</f>
+        <f>Assumptions!$C$62</f>
         <v/>
       </c>
     </row>
@@ -2771,7 +2714,7 @@
         </is>
       </c>
       <c r="C10" s="13">
-        <f>Assumptions!$C$60*Assumptions!$C$61/1000</f>
+        <f>Assumptions!$C$62*Assumptions!$C$63/1000</f>
         <v/>
       </c>
     </row>
@@ -2822,28 +2765,28 @@
     <row r="17">
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>MHO is a well-run, net-cash builder buying back 5% of its shares a year, and at 1.16x book it is not expensive. But it now earns</t>
+          <t>MHO is a well-run, net-cash builder buying back 5% of its shares a year, and at 1.10x book it is not expensive. But it now earns</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>roughly its cost of equity. Return on equity has fallen to 9.4% on trailing numbers, and at a 11.8% cost of equity today's</t>
+          <t>roughly its cost of equity. Return on equity has fallen to 9.3% on trailing numbers, and at a 12.0% cost of equity today's</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>multiple already pays for a normalised return near 13%. My base case reaches only 10.8% by 2028, and only by assuming a</t>
+          <t>multiple already pays for a normalised return near 13%. My base case reaches only 9.8% by 2028, and only by assuming a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>competitive recovery I cannot verify. I initiate at Underweight: the margin recovery is priced but not yet earned.</t>
+          <t>competitive recovery I cannot verify. I initiate at Neutral: the margin recovery is priced but not yet earned.</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2840,7 @@
         </is>
       </c>
       <c r="C24" s="11">
-        <f>DCF!$C$44*(1+DCF!$C$9/100)</f>
+        <f>DCF!$C$47*(1+DCF!$C$9/100)</f>
         <v/>
       </c>
       <c r="E24" s="16">
@@ -2924,7 +2867,7 @@
         </is>
       </c>
       <c r="C25" s="11">
-        <f>Comps!H35</f>
+        <f>Comps!H34</f>
         <v/>
       </c>
       <c r="E25" s="16">
@@ -3036,16 +2979,16 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>16.19294706284738</v>
+        <v>15.82686218394968</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>26.14913067485417</v>
+        <v>25.98113220025009</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>0.1258466063643327</v>
+        <v>0.1210539027941942</v>
       </c>
       <c r="F31" s="25" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="G31" s="26">
         <f>F31/$C$8-1</f>
@@ -3064,16 +3007,16 @@
         </is>
       </c>
       <c r="C32" s="28" t="n">
-        <v>14.06119322936485</v>
+        <v>13.14864821008826</v>
       </c>
       <c r="D32" s="28" t="n">
-        <v>21.15692798587284</v>
+        <v>19.23698646428809</v>
       </c>
       <c r="E32" s="29" t="n">
-        <v>0.1084713042026645</v>
+        <v>0.09828226077143039</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G32" s="31">
         <f>F32/$C$8-1</f>
@@ -3092,16 +3035,16 @@
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>9.529085045303544</v>
+        <v>9.176772774107896</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>9.886166281029503</v>
+        <v>9.262716988048123</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>0.06694434902229758</v>
+        <v>0.06218324744170975</v>
       </c>
       <c r="F33" s="25" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G33" s="26">
         <f>F33/$C$8-1</f>
@@ -3443,7 +3386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L61"/>
+  <dimension ref="B2:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.2" customWidth="1" min="1" max="1"/>
@@ -3544,32 +3487,32 @@
         </is>
       </c>
       <c r="C8" s="39" t="n">
-        <v>6.81</v>
+        <v>6.807</v>
       </c>
       <c r="D8" s="39" t="n">
-        <v>6.8</v>
+        <v>6.721</v>
       </c>
       <c r="E8" s="39" t="n">
-        <v>6.72</v>
+        <v>6.595</v>
       </c>
       <c r="F8" s="39" t="n">
-        <v>6.65</v>
+        <v>6.49</v>
       </c>
       <c r="G8" s="39" t="n">
-        <v>6.35</v>
+        <v>6.76</v>
       </c>
       <c r="H8" s="39" t="n">
-        <v>6.1</v>
+        <v>6.76</v>
       </c>
       <c r="I8" s="39" t="n">
-        <v>5.95</v>
+        <v>6.76</v>
       </c>
       <c r="J8" s="39" t="n">
-        <v>5.9</v>
+        <v>6.76</v>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>2023–25 actual (FRED MORTGAGE30US annual avg). 2026E+ forecast. Spot = 6.71% at 03-Sep-2026.</t>
+          <t>2023-25 actual: calendar-year average of FRED MORTGAGE30US, pulled 11-Sep-2026. These were previously entered lagged one year. 2026E is 36 weeks observed plus the spot held to year end. 2027E+ HOLDS THE SPOT of 6.76% (2026-09-10): I do not forecast rates, so the target carries no rate view. The previous path declined to 5.90%, which implied the 10-yr Treasury falling to about 4.09% and was worth roughly $7/share.</t>
         </is>
       </c>
     </row>
@@ -3588,257 +3531,248 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="15.5" customHeight="1">
-      <c r="B11" s="3" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Inflation (%)</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>THE SINGLE INFLATION INPUT. Every nominal dollar driver below is grown from its 2025 actual at this rate, and it is also the terminal growth rate, so one number governs both — flex it here and it propagates. Ratio drivers are NOT inflated: a ratio is inflation-neutral by construction, so they are held at their most recent observed level instead. Measured CPI over the year to Q2-2026 was 3.8%; using that instead of 2.50% moves the DCF by about $0.34 and would contradict the terminal growth rate, so it is not worth the inconsistency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Real growth in perpetuity (%)</t>
+        </is>
+      </c>
+      <c r="C11" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>Real growth ON TOP of inflation, in perpetuity. Terminal growth is not a separate input: it is derived as inflation + real growth = 2.50% + 0.00% = 2.50%, so the two cannot drift apart. Zero real growth is a deliberate, conservative choice — it says the company grows with prices but not faster, shrinking slowly against a growing economy. Each 50bp here is worth roughly $3.50 a share; see the WACC x terminal growth grid on the DCF sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="6" customHeight="1"/>
+    <row r="13" ht="15.5" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>INCENTIVE INTENSITY  —  incentive load (% of gross ASP) = base + rate slope x (mortgage rate − neutral) + competition premium</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="14" t="inlineStr">
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Northern — base incentive (% of gross ASP)</t>
         </is>
       </c>
-      <c r="C12" s="39" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Northern — rate slope (pp per 100bp above neutral)</t>
-        </is>
-      </c>
-      <c r="C13" s="40" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="38" t="inlineStr">
-        <is>
-          <t>Northern — competition premium (pp)</t>
-        </is>
-      </c>
       <c r="C14" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="39" t="n">
-        <v>1.209</v>
-      </c>
-      <c r="F14" s="39" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="G14" s="39" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="H14" s="39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I14" s="39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J14" s="39" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>Incentive over and above what the rate alone justifies. Zero through 2025 by construction — the Northern margin held.</t>
-        </is>
+        <v>1.015</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="14" t="inlineStr">
         <is>
+          <t>Northern — rate slope (pp per 100bp above neutral)</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>Northern — competition premium (pp)</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="39" t="n">
+        <v>1.256</v>
+      </c>
+      <c r="F16" s="39" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="G16" s="39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H16" s="39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I16" s="39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J16" s="39" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>Incentive over and above what the rate alone justifies. Zero in 2023-24 by construction. The 1.26pp for 2025 is NOT assumed: the 10-K discloses Northern per-home incentives rose $6.5k while mortgage rates FELL (6.80%-&gt;6.72%), so the rate term cannot account for it and the residual is forced positive. 2026E+ (3.51pp falling to 2.65pp) is forecast, not calibrated, and is the least defended input in the model - the note argues a competition story for the South, not the North. Holding it at the 2025 level instead raises 2027E EPS by about $1.07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="14" t="inlineStr">
+        <is>
           <t>Southern — base incentive (% of gross ASP)</t>
         </is>
       </c>
-      <c r="C15" s="39" t="n">
-        <v>1.944</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="14" t="inlineStr">
+      <c r="C17" s="39" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Southern — rate slope (pp per 100bp above neutral)</t>
         </is>
       </c>
-      <c r="C16" s="40" t="n">
+      <c r="C18" s="40" t="n">
         <v>1.2</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="38" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>Southern — competition premium (pp)</t>
         </is>
       </c>
-      <c r="C17" s="39" t="n">
+      <c r="C19" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D19" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="39" t="n">
-        <v>1.972</v>
-      </c>
-      <c r="F17" s="39" t="n">
+      <c r="E19" s="39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F19" s="39" t="n">
         <v>4.371</v>
       </c>
-      <c r="G17" s="39" t="n">
+      <c r="G19" s="39" t="n">
         <v>3.75</v>
       </c>
-      <c r="H17" s="39" t="n">
+      <c r="H19" s="39" t="n">
         <v>3.3</v>
       </c>
-      <c r="I17" s="39" t="n">
+      <c r="I19" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="39" t="n">
+      <c r="J19" s="39" t="n">
         <v>2.8</v>
       </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>THE KEY INPUT. 3.6pp in 2025 and 6.0pp in 2026E: mortgage rates were flat 2024→2025, so the Southern margin collapse is a supply/competition event, not a rate event. Flex this before anything else.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="6" customHeight="1"/>
-    <row r="19" ht="15.5" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>THE KEY INPUT, and the three years are known with very different confidence. 2023-24: zero by construction, the base period. 2025 (2.04pp): CALIBRATED, not chosen - solved together with the base rate from four figures the 10-K discloses (total incentives of $131.3m in 2024 and $200.0m in 2025, and per-home increases of $6.5k Northern and $8.8k Southern). Mortgage rates FELL 12.6bp over that year, so a rate-only model predicts incentives easing when they in fact nearly doubled. 2026 (4.37pp): NOT calibrated - MHO discloses incentives annually, not quarterly, so there is nothing to solve against. It is set by hand so the full year lands near reported 1H26 margin and ASP. 2027-30: JUDGEMENT. A decay of about 11%/yr that never reaches zero, still carrying 2.80pp in 2030. Nothing observable supports the shape; it is the single least defended input in the model and the reason the sensitivity grid matters more than the point estimate. Flex this before anything else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="15.5" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>VOLUME, PRICE AND COST  (growth rates, % — projections only)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="38" t="inlineStr">
-        <is>
-          <t>Deliveries growth — Northern (%)</t>
-        </is>
-      </c>
-      <c r="F20" s="39" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="G20" s="39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H20" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="I20" s="39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J20" s="39" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="38" t="inlineStr">
-        <is>
-          <t>Deliveries growth — Southern (%)</t>
-        </is>
-      </c>
-      <c r="F21" s="39" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="G21" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" s="39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I21" s="39" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="J21" s="39" t="n">
-        <v>4</v>
-      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="38" t="inlineStr">
         <is>
-          <t>Gross ASP growth — Northern (%)</t>
+          <t>Deliveries growth — Northern (%)</t>
         </is>
       </c>
       <c r="F22" s="39" t="n">
-        <v>1</v>
+        <v>-3.9</v>
       </c>
       <c r="G22" s="39" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="H22" s="39" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="I22" s="39" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="J22" s="39" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Gross ASP = list price before incentives.</t>
+          <t>2026E is set by hand so the full year lands near reported 1H 2026 (4,120 deliveries, $459k ASP, $5.57 EPS, 22.1% reported gross margin) — it is NOT solved from those figures, it is eyeballed against them. 2027E+ is judgement with no external anchor: see README, Tier 3. Full-year 2026E implies a 2H 7.6% above 1H, against an actual 6.3% step in 2025.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="38" t="inlineStr">
         <is>
-          <t>Gross ASP growth — Southern (%)</t>
+          <t>Deliveries growth — Southern (%)</t>
         </is>
       </c>
       <c r="F23" s="39" t="n">
-        <v>-1.5</v>
+        <v>-4.3</v>
       </c>
       <c r="G23" s="39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H23" s="39" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="I23" s="39" t="n">
-        <v>2.25</v>
+        <v>4.25</v>
       </c>
       <c r="J23" s="39" t="n">
-        <v>2.25</v>
+        <v>4</v>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026E is set by hand so the full year lands near reported 1H 2026 (4,120 deliveries, $459k ASP, $5.57 EPS, 22.1% reported gross margin) — it is NOT solved from those figures, it is eyeballed against them. 2027E+ is judgement with no external anchor: see README, Tier 3. </t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="38" t="inlineStr">
         <is>
-          <t>Cost per home growth — Northern (%)</t>
+          <t>Gross ASP growth — Northern (%)</t>
         </is>
       </c>
       <c r="F24" s="39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="39" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="H24" s="39" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="I24" s="39" t="n">
         <v>2.5</v>
@@ -3846,663 +3780,792 @@
       <c r="J24" s="39" t="n">
         <v>2.5</v>
       </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gross ASP = list price before incentives. 2026E is set by hand so the full year lands near reported 1H 2026 (4,120 deliveries, $459k ASP, $5.57 EPS, 22.1% reported gross margin) — it is NOT solved from those figures, it is eyeballed against them. 2027E+ is judgement with no external anchor: see README, Tier 3. </t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="38" t="inlineStr">
         <is>
+          <t>Gross ASP growth — Southern (%)</t>
+        </is>
+      </c>
+      <c r="F25" s="39" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G25" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J25" s="39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026E is set by hand so the full year lands near reported 1H 2026 (4,120 deliveries, $459k ASP, $5.57 EPS, 22.1% reported gross margin) — it is NOT solved from those figures, it is eyeballed against them. 2027E+ is judgement with no external anchor: see README, Tier 3. </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="38" t="inlineStr">
+        <is>
+          <t>Cost per home growth — Northern (%)</t>
+        </is>
+      </c>
+      <c r="F26" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H26" s="39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I26" s="39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J26" s="39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026E is set by hand so the full year lands near reported 1H 2026 (4,120 deliveries, $459k ASP, $5.57 EPS, 22.1% reported gross margin) — it is NOT solved from those figures, it is eyeballed against them. 2027E+ is judgement with no external anchor: see README, Tier 3. </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="38" t="inlineStr">
+        <is>
           <t>Cost per home growth — Southern (%)</t>
         </is>
       </c>
-      <c r="F25" s="39" t="n">
+      <c r="F27" s="39" t="n">
         <v>-0.3</v>
       </c>
-      <c r="G25" s="39" t="n">
+      <c r="G27" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="39" t="n">
+      <c r="H27" s="39" t="n">
         <v>2.3</v>
       </c>
-      <c r="I25" s="39" t="n">
+      <c r="I27" s="39" t="n">
         <v>2.5</v>
       </c>
-      <c r="J25" s="39" t="n">
+      <c r="J27" s="39" t="n">
         <v>2.5</v>
       </c>
-      <c r="L25" s="9" t="inlineStr">
-        <is>
-          <t>Land + stick-and-brick + closing cost per unit delivered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="6" customHeight="1"/>
-    <row r="27" ht="15.5" customHeight="1">
-      <c r="B27" s="3" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Land + stick-and-brick + closing cost per unit delivered. 2026E is set by hand so the full year lands near reported 1H 2026 (4,120 deliveries, $459k ASP, $5.57 EPS, 22.1% reported gross margin) — it is NOT solved from those figures, it is eyeballed against them. 2027E+ is judgement with no external anchor: see README, Tier 3. </t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="6" customHeight="1"/>
+    <row r="29" ht="15.5" customHeight="1">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>OTHER INCOME STATEMENT DRIVERS</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
-      <c r="J27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="38" t="inlineStr">
-        <is>
-          <t>Land sale revenue ($000)</t>
-        </is>
-      </c>
-      <c r="F28" s="41" t="n">
-        <v>22000</v>
-      </c>
-      <c r="G28" s="41" t="n">
-        <v>24000</v>
-      </c>
-      <c r="H28" s="41" t="n">
-        <v>26000</v>
-      </c>
-      <c r="I28" s="41" t="n">
-        <v>28000</v>
-      </c>
-      <c r="J28" s="41" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="38" t="inlineStr">
-        <is>
-          <t>Financial services revenue growth (%)</t>
-        </is>
-      </c>
-      <c r="F29" s="39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G29" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="H29" s="39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I29" s="39" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J29" s="39" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="38" t="inlineStr">
         <is>
-          <t>Selling expense (% of homebuilding revenue)</t>
-        </is>
-      </c>
-      <c r="F30" s="39" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G30" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="H30" s="39" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I30" s="39" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J30" s="39" t="n">
-        <v>5.65</v>
+          <t>Land sale revenue ($000)</t>
+        </is>
+      </c>
+      <c r="F30" s="41" t="n">
+        <v>18085.1</v>
+      </c>
+      <c r="G30" s="41" t="n">
+        <v>18537.2</v>
+      </c>
+      <c r="H30" s="41" t="n">
+        <v>19000.7</v>
+      </c>
+      <c r="I30" s="41" t="n">
+        <v>19475.7</v>
+      </c>
+      <c r="J30" s="41" t="n">
+        <v>19962.6</v>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>Grown from its 2025 actual at the single inflation input above (the nominal rule) — not a hand-set path. 2025 actual $17.6m. Land sales are incidental to the thesis; this line is small and is not forecast independently.</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="38" t="inlineStr">
         <is>
-          <t>Homebuilding G&amp;A (% of homebuilding revenue)</t>
+          <t>Financial services revenue growth (%)</t>
         </is>
       </c>
       <c r="F31" s="39" t="n">
-        <v>2.8</v>
+        <v>-4.1</v>
       </c>
       <c r="G31" s="39" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="H31" s="39" t="n">
-        <v>2.66</v>
+        <v>4.75</v>
       </c>
       <c r="I31" s="39" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="J31" s="39" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>DERIVED, not assumed: financial services originates mortgages for buyers of these homes, so its revenue tracks deliveries. This row is the average of the two delivery growth rates above and moves with them automatically.</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="38" t="inlineStr">
         <is>
-          <t>Corporate / unallocated ($000)</t>
-        </is>
-      </c>
-      <c r="F32" s="41" t="n">
-        <v>-93000</v>
-      </c>
-      <c r="G32" s="41" t="n">
-        <v>-96500</v>
-      </c>
-      <c r="H32" s="41" t="n">
-        <v>-100500</v>
-      </c>
-      <c r="I32" s="41" t="n">
-        <v>-104500</v>
-      </c>
-      <c r="J32" s="41" t="n">
-        <v>-108500</v>
+          <t>Selling expense (% of homebuilding revenue)</t>
+        </is>
+      </c>
+      <c r="F32" s="39" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="G32" s="39" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="H32" s="39" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="I32" s="39" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="J32" s="39" t="n">
+        <v>6.22</v>
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>Not charged to either region in the 10-K segment note; averaged −$85m over 2023–25.</t>
+          <t>Held flat at the most recent observed level (the ratio rule): a ratio is inflation-neutral, so holding it IS the inflation adjustment. Held at 6.22%, the 1H 2026 actual ($119.4m on $1,920.4m of homebuilding revenue) rather than the 5.72% of FY2025 — using the older figure would override reported data.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="38" t="inlineStr">
         <is>
-          <t>Inventory impairment &amp; write-offs ($000)</t>
-        </is>
-      </c>
-      <c r="F33" s="41" t="n">
-        <v>16000</v>
-      </c>
-      <c r="G33" s="41" t="n">
-        <v>9000</v>
-      </c>
-      <c r="H33" s="41" t="n">
-        <v>7000</v>
-      </c>
-      <c r="I33" s="41" t="n">
-        <v>7000</v>
-      </c>
-      <c r="J33" s="41" t="n">
-        <v>7000</v>
+          <t>Homebuilding G&amp;A (% of homebuilding revenue)</t>
+        </is>
+      </c>
+      <c r="F33" s="39" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G33" s="39" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H33" s="39" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I33" s="39" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J33" s="39" t="n">
+        <v>2.76</v>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>$47.7m in 2025, of which $41.0m Southern.</t>
+          <t>Held flat at the most recent observed level (the ratio rule): a ratio is inflation-neutral, so holding it IS the inflation adjustment. Held at 2.76%, the FY2025 actual. Total company G&amp;A is running flat year-on-year in 1H26, which is consistent with this.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="38" t="inlineStr">
         <is>
+          <t>Corporate / unallocated ($000)</t>
+        </is>
+      </c>
+      <c r="F34" s="41" t="n">
+        <v>-91872.8</v>
+      </c>
+      <c r="G34" s="41" t="n">
+        <v>-94169.60000000001</v>
+      </c>
+      <c r="H34" s="41" t="n">
+        <v>-96523.89999999999</v>
+      </c>
+      <c r="I34" s="41" t="n">
+        <v>-98937</v>
+      </c>
+      <c r="J34" s="41" t="n">
+        <v>-101410.4</v>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>Grown from its 2025 actual at the single inflation input above (the nominal rule) — not a hand-set path. 2025 actual −$89.6m (total operating income less the three segments). Not charged to either region in the 10-K segment note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="38" t="inlineStr">
+        <is>
+          <t>Inventory impairment &amp; write-offs ($000)</t>
+        </is>
+      </c>
+      <c r="F35" s="41" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G35" s="41" t="n">
+        <v>9000</v>
+      </c>
+      <c r="H35" s="41" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I35" s="41" t="n">
+        <v>7000</v>
+      </c>
+      <c r="J35" s="41" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>$47.7m in 2025, of which $41.0m Southern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="38" t="inlineStr">
+        <is>
           <t>Net interest income ($000)</t>
         </is>
       </c>
-      <c r="F34" s="41" t="n">
+      <c r="F36" s="41" t="n">
         <v>18000</v>
       </c>
-      <c r="G34" s="41" t="n">
-        <v>16000</v>
-      </c>
-      <c r="H34" s="41" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I34" s="41" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J34" s="41" t="n">
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>Land sale gross margin (%)</t>
-        </is>
-      </c>
-      <c r="C35" s="39" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>Share of land revenue in Southern (%)</t>
-        </is>
-      </c>
-      <c r="C36" s="42" t="n">
-        <v>65</v>
+      <c r="G36" s="41" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H36" s="41" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I36" s="41" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J36" s="41" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>Held flat. Depends on the cash balance and short rates, neither of which this model forecasts; it is small enough that a path would be false precision.</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Financial services pre-tax margin (%)</t>
+          <t>Land sale gross margin (%)</t>
         </is>
       </c>
       <c r="C37" s="39" t="n">
-        <v>54.5</v>
+        <v>7</v>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>54.3% in 2025 (op income $68.2m on revenue $125.5m).</t>
+          <t>Land sales carried a 24% gross margin in 2025 and 29% in 2024, but on only $17.6m and $12.6m of revenue. 7% is deliberately conservative on a line too small to matter.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="14" t="inlineStr">
         <is>
+          <t>Share of land revenue in Southern (%)</t>
+        </is>
+      </c>
+      <c r="C38" s="42" t="n">
+        <v>65</v>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>NOT DISCLOSED. The 10-K segment note gives total segment revenue only, so land sales cannot be split by region from the filings. This input does that split, and it matters because segment revenue includes land sales while average selling price must not. Moving it from 0% to 100% Southern changes the two-year Southern price decline by about $2k a home, so the thesis does not turn on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Financial services pre-tax margin (%)</t>
+        </is>
+      </c>
+      <c r="C39" s="39" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>54.3% in 2025 (op income $68.2m on revenue $125.5m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="14" t="inlineStr">
+        <is>
           <t>Effective tax rate (%)</t>
         </is>
       </c>
-      <c r="C38" s="39" t="n">
+      <c r="C40" s="39" t="n">
         <v>23.5</v>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>23.5% vs 23.5% in 2025; energy-efficiency credits keep it below statutory + state.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="6" customHeight="1"/>
-    <row r="40" ht="15.5" customHeight="1">
-      <c r="B40" s="3" t="inlineStr">
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="15.5" customHeight="1">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>BALANCE SHEET &amp; CASH FLOW DRIVERS</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="38" t="inlineStr">
-        <is>
-          <t>Inventory turns (homebuilding revenue / ending inventory)</t>
-        </is>
-      </c>
-      <c r="F41" s="40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G41" s="40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="H41" s="40" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I41" s="40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J41" s="40" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="L41" s="9" t="inlineStr">
-        <is>
-          <t>1.27x in 2025. Falls in 2026E as deliveries drop faster than the land pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="38" t="inlineStr">
-        <is>
-          <t>Other operating assets (% of revenue)</t>
-        </is>
-      </c>
-      <c r="F42" s="39" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G42" s="39" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="H42" s="39" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="I42" s="39" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="J42" s="39" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="C42" s="3" t="n"/>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="38" t="inlineStr">
         <is>
-          <t>Other liabilities (% of revenue)</t>
-        </is>
-      </c>
-      <c r="F43" s="39" t="n">
-        <v>14.45</v>
-      </c>
-      <c r="G43" s="39" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H43" s="39" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="I43" s="39" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="J43" s="39" t="n">
-        <v>14.55</v>
+          <t>Inventory turns (homebuilding revenue / ending inventory)</t>
+        </is>
+      </c>
+      <c r="F43" s="40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G43" s="40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H43" s="40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I43" s="40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J43" s="40" t="n">
+        <v>1.27</v>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
-          <t>A/P, accrued comp, customer deposits, warranty reserve. 14.4% in 2025.</t>
+          <t>1.27x in 2025. Falls in 2026E as deliveries drop faster than the land pipeline.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="38" t="inlineStr">
         <is>
-          <t>Capital expenditure ($000)</t>
-        </is>
-      </c>
-      <c r="F44" s="41" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G44" s="41" t="n">
-        <v>11500</v>
-      </c>
-      <c r="H44" s="41" t="n">
-        <v>12000</v>
-      </c>
-      <c r="I44" s="41" t="n">
-        <v>12500</v>
-      </c>
-      <c r="J44" s="41" t="n">
-        <v>13000</v>
+          <t>Other operating assets (% of revenue)</t>
+        </is>
+      </c>
+      <c r="F44" s="39" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="G44" s="39" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="H44" s="39" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="I44" s="39" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="J44" s="39" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>Held flat at the most recent observed level (the ratio rule): a ratio is inflation-neutral, so holding it IS the inflation adjustment. Held at 14.35%, the 2025 actual.</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="38" t="inlineStr">
         <is>
-          <t>Depreciation &amp; amortisation ($000)</t>
-        </is>
-      </c>
-      <c r="F45" s="41" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G45" s="41" t="n">
-        <v>21000</v>
-      </c>
-      <c r="H45" s="41" t="n">
-        <v>22000</v>
-      </c>
-      <c r="I45" s="41" t="n">
-        <v>23000</v>
-      </c>
-      <c r="J45" s="41" t="n">
-        <v>24000</v>
+          <t>Other liabilities (% of revenue)</t>
+        </is>
+      </c>
+      <c r="F45" s="39" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="G45" s="39" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="H45" s="39" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="I45" s="39" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="J45" s="39" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>A/P, accrued comp, customer deposits, warranty reserve. 14.4% in 2025.</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="38" t="inlineStr">
         <is>
-          <t>Stock-based compensation ($000)</t>
+          <t>Capital expenditure ($000)</t>
         </is>
       </c>
       <c r="F46" s="41" t="n">
-        <v>17500</v>
+        <v>9849.200000000001</v>
       </c>
       <c r="G46" s="41" t="n">
-        <v>18000</v>
+        <v>10095.5</v>
       </c>
       <c r="H46" s="41" t="n">
-        <v>18500</v>
+        <v>10347.8</v>
       </c>
       <c r="I46" s="41" t="n">
-        <v>19000</v>
+        <v>10606.5</v>
       </c>
       <c r="J46" s="41" t="n">
-        <v>19500</v>
+        <v>10871.7</v>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>Grown from its 2025 actual at the single inflation input above (the nominal rule) — not a hand-set path. 2025 actual $9.6m. Real investment for a builder is land, which sits in inventory, not here.</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="38" t="inlineStr">
         <is>
-          <t>Share repurchase ($000)</t>
+          <t>Depreciation &amp; amortisation ($000)</t>
         </is>
       </c>
       <c r="F47" s="41" t="n">
-        <v>185000</v>
+        <v>19370.4</v>
       </c>
       <c r="G47" s="41" t="n">
-        <v>185000</v>
+        <v>19854.7</v>
       </c>
       <c r="H47" s="41" t="n">
-        <v>185000</v>
+        <v>20351.1</v>
       </c>
       <c r="I47" s="41" t="n">
-        <v>185000</v>
+        <v>20859.9</v>
       </c>
       <c r="J47" s="41" t="n">
-        <v>185000</v>
+        <v>21381.4</v>
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>$202m in 2025, $177m in 2024. Assumes management sustains the pace.</t>
+          <t>Grown from its 2025 actual at the single inflation input above (the nominal rule) — not a hand-set path. 2025 actual $18.9m.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="38" t="inlineStr">
         <is>
-          <t>Average repurchase price ($)</t>
-        </is>
-      </c>
-      <c r="F48" s="43" t="n">
-        <v>150</v>
-      </c>
-      <c r="G48" s="43" t="n">
-        <v>161</v>
-      </c>
-      <c r="H48" s="43" t="n">
-        <v>174</v>
-      </c>
-      <c r="I48" s="43" t="n">
-        <v>187</v>
-      </c>
-      <c r="J48" s="43" t="n">
-        <v>200</v>
+          <t>Stock-based compensation ($000)</t>
+        </is>
+      </c>
+      <c r="F48" s="41" t="n">
+        <v>17422.9</v>
+      </c>
+      <c r="G48" s="41" t="n">
+        <v>17858.5</v>
+      </c>
+      <c r="H48" s="41" t="n">
+        <v>18305</v>
+      </c>
+      <c r="I48" s="41" t="n">
+        <v>18762.6</v>
+      </c>
+      <c r="J48" s="41" t="n">
+        <v>19231.7</v>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>Grown from its 2025 actual at the single inflation input above (the nominal rule) — not a hand-set path. 2025 actual $17.0m. Treated as a real cost and deducted in the free cash flow build.</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="38" t="inlineStr">
         <is>
-          <t>Option / RSU issuance (000 shares)</t>
+          <t>Share repurchase ($000)</t>
         </is>
       </c>
       <c r="F49" s="41" t="n">
-        <v>150</v>
+        <v>185000</v>
       </c>
       <c r="G49" s="41" t="n">
-        <v>150</v>
+        <v>185000</v>
       </c>
       <c r="H49" s="41" t="n">
-        <v>150</v>
+        <v>185000</v>
       </c>
       <c r="I49" s="41" t="n">
-        <v>150</v>
+        <v>185000</v>
       </c>
       <c r="J49" s="41" t="n">
-        <v>150</v>
+        <v>185000</v>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>$202m in 2025, $177m in 2024. Assumes management sustains the pace.</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="38" t="inlineStr">
         <is>
-          <t>Homebuilding debt ($000)</t>
-        </is>
-      </c>
-      <c r="F50" s="41" t="n">
-        <v>696500</v>
-      </c>
-      <c r="G50" s="41" t="n">
-        <v>696500</v>
-      </c>
-      <c r="H50" s="41" t="n">
-        <v>696500</v>
-      </c>
-      <c r="I50" s="41" t="n">
-        <v>550000</v>
-      </c>
-      <c r="J50" s="41" t="n">
-        <v>550000</v>
+          <t>Average repurchase price ($)</t>
+        </is>
+      </c>
+      <c r="F50" s="43" t="n">
+        <v>140.07</v>
+      </c>
+      <c r="G50" s="43" t="n">
+        <v>140.07</v>
+      </c>
+      <c r="H50" s="43" t="n">
+        <v>140.07</v>
+      </c>
+      <c r="I50" s="43" t="n">
+        <v>140.07</v>
+      </c>
+      <c r="J50" s="43" t="n">
+        <v>140.07</v>
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>Senior notes. 2029E step-down assumes the 2028 maturity is partly repaid from cash.</t>
+          <t>HELD AT THE CURRENT MARKET PRICE. This model does not forecast the share price. The previous path ramped $150 to $200, which assumed the stock rises 35% while the note argues it is worth less than it trades for today — internally inconsistent. It affects reported EPS in the outer years (shares retired = buyback / this price) but not the DCF or the target.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="38" t="inlineStr">
         <is>
+          <t>Option / RSU issuance (000 shares)</t>
+        </is>
+      </c>
+      <c r="F51" s="41" t="n">
+        <v>150</v>
+      </c>
+      <c r="G51" s="41" t="n">
+        <v>150</v>
+      </c>
+      <c r="H51" s="41" t="n">
+        <v>150</v>
+      </c>
+      <c r="I51" s="41" t="n">
+        <v>150</v>
+      </c>
+      <c r="J51" s="41" t="n">
+        <v>150</v>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>Held flat at 150k shares a year, roughly the recent run-rate. A unit count, so nothing to inflate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="38" t="inlineStr">
+        <is>
+          <t>Homebuilding debt ($000)</t>
+        </is>
+      </c>
+      <c r="F52" s="41" t="n">
+        <v>696500</v>
+      </c>
+      <c r="G52" s="41" t="n">
+        <v>696500</v>
+      </c>
+      <c r="H52" s="41" t="n">
+        <v>696500</v>
+      </c>
+      <c r="I52" s="41" t="n">
+        <v>550000</v>
+      </c>
+      <c r="J52" s="41" t="n">
+        <v>550000</v>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>CONTRACTUAL, not a growth assumption and not inflated — you owe the face amount until it matures. Two senior notes: $400.0m of 4.95% notes due 2028 and $300.0m of 3.95% notes due 2030, carried at $696.5m net of unamortised issuance cost. The 2029 step-down assumes roughly $150m of the 2028 maturity is retired from cash and the rest refinanced; MHO held $735.9m of cash against $696.9m of debt at 30-Jun-26, so full repayment is affordable and this is the middle course.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="38" t="inlineStr">
+        <is>
           <t>Financial services debt ($000)</t>
         </is>
       </c>
-      <c r="F51" s="41" t="n">
-        <v>290000</v>
-      </c>
-      <c r="G51" s="41" t="n">
-        <v>305000</v>
-      </c>
-      <c r="H51" s="41" t="n">
-        <v>322000</v>
-      </c>
-      <c r="I51" s="41" t="n">
-        <v>336000</v>
-      </c>
-      <c r="J51" s="41" t="n">
-        <v>351000</v>
-      </c>
-      <c r="L51" s="9" t="inlineStr">
-        <is>
-          <t>Mortgage warehouse facilities — matched by loans held for sale; excluded from net debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="14" t="inlineStr">
+      <c r="F53" s="41" t="n">
+        <v>258448</v>
+      </c>
+      <c r="G53" s="41" t="n">
+        <v>274124</v>
+      </c>
+      <c r="H53" s="41" t="n">
+        <v>294507</v>
+      </c>
+      <c r="I53" s="41" t="n">
+        <v>313666</v>
+      </c>
+      <c r="J53" s="41" t="n">
+        <v>333000</v>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>DERIVED, not assumed: mortgage warehouse facilities fund closings on the builder own homes, so the balance scales with homebuilding revenue at 6.45% — the 2025 actual ($277m on $4,292m); 2024 was 6.52%. Matched by loans held for sale and excluded from net debt. Not inflated: this is a funding line tied to volume, not a price-level cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>Property &amp; equipment at 31-Dec-2025 ($000)</t>
         </is>
       </c>
-      <c r="C52" s="41" t="n">
+      <c r="C54" s="41" t="n">
         <v>70000</v>
       </c>
-    </row>
-    <row r="53" ht="6" customHeight="1"/>
-    <row r="54" ht="15.5" customHeight="1">
-      <c r="B54" s="3" t="inlineStr">
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>Opening balance only, not a driver. Property and equipment is carried outside inventory and is immaterial for a builder; it exists so the balance sheet ties. Capex and depreciation above move it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="6" customHeight="1"/>
+    <row r="56" ht="15.5" customHeight="1">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>VALUATION INPUTS</t>
         </is>
       </c>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="n"/>
-      <c r="F54" s="3" t="n"/>
-      <c r="G54" s="3" t="n"/>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="3" t="n"/>
-    </row>
-    <row r="55">
-      <c r="B55" s="14" t="inlineStr">
-        <is>
-          <t>Risk-free rate — 10-yr UST (%)</t>
-        </is>
-      </c>
-      <c r="C55" s="39" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>FRED DGS10, 02-Sep-2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>Equity risk premium (%)</t>
-        </is>
-      </c>
-      <c r="C56" s="39" t="n">
-        <v>5</v>
-      </c>
+      <c r="C56" s="3" t="n"/>
+      <c r="D56" s="3" t="n"/>
+      <c r="E56" s="3" t="n"/>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Beta (levered)</t>
-        </is>
-      </c>
-      <c r="C57" s="40" t="n">
-        <v>1.41</v>
+          <t>Risk-free rate — 10-yr UST (%)</t>
+        </is>
+      </c>
+      <c r="C57" s="39" t="n">
+        <v>4.95</v>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Blume-adjusted: 0.67 x the published 5-yr raw beta of 1.61, + 0.33 x 1.0. Raw historical betas are noisy and mean-revert, which is why Bloomberg reports the adjusted figure.</t>
+          <t>FRED DGS10, 11-Sep-2026. 30-yr UST 5.37% the same day. Pulled 11-Sep-2026.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Pre-tax cost of debt (%)</t>
+          <t>Equity risk premium (%)</t>
         </is>
       </c>
       <c r="C58" s="39" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>BB index effective yield 6.03% (FRED BAMLH0A1HYBBEY) + 22bp. MHO upgraded to BB+ in 2026.</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>Terminal growth rate (%)</t>
-        </is>
-      </c>
-      <c r="C59" s="39" t="n">
-        <v>2.5</v>
+          <t>Beta (levered)</t>
+        </is>
+      </c>
+      <c r="C59" s="40" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Blume-adjusted: 0.67 x the published 5-yr raw beta of 1.61, + 0.33 x 1.0. Raw historical betas are noisy and mean-revert, which is why Bloomberg reports the adjusted figure.</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>Share price ($)</t>
-        </is>
-      </c>
-      <c r="C60" s="25" t="n">
-        <v>148.26</v>
+          <t>Pre-tax cost of debt (%)</t>
+        </is>
+      </c>
+      <c r="C60" s="39" t="n">
+        <v>6.25</v>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>stockanalysis.com, 04-Sep-2026 11:44 ET.</t>
+          <t>BB index effective yield (FRED BAMLH0A1HYBBEY) + 22bp. MHO upgraded to BB+ in 2026. Pulled 11-Sep-2026.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="14" t="inlineStr">
         <is>
+          <t>Terminal growth rate (%)</t>
+        </is>
+      </c>
+      <c r="C61" s="39" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Share price ($)</t>
+        </is>
+      </c>
+      <c r="C62" s="25" t="n">
+        <v>140.07</v>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>stockanalysis.com, 04-Sep-2026 11:44 ET. Rates on this sheet were refreshed 11-Sep-2026; the share price was not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="14" t="inlineStr">
+        <is>
           <t>Shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C61" s="41" t="n">
+      <c r="C63" s="41" t="n">
         <v>25276</v>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>Per Q2-26 10-Q cover.</t>
         </is>
@@ -4520,7 +4583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L78"/>
+  <dimension ref="B2:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.2" customWidth="1" min="1" max="1"/>
@@ -4834,925 +4897,962 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22" ht="15.5" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which: land sale revenue (company total)</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="n">
+        <v>25301</v>
+      </c>
+      <c r="D21" s="41" t="n">
+        <v>12635</v>
+      </c>
+      <c r="E21" s="41" t="n">
+        <v>17644</v>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>FY23/24/25 8-K Ex-99.1, "Land revenue". Segment revenue above INCLUDES this; it is not a home price. Not disclosed by segment, so it is split on the Assumptions land-split input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which: land sale gross profit (company total)</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="n">
+        <v>3360</v>
+      </c>
+      <c r="D22" s="41" t="n">
+        <v>3709</v>
+      </c>
+      <c r="E22" s="41" t="n">
+        <v>4196</v>
+      </c>
+    </row>
+    <row r="23" ht="6" customHeight="1"/>
+    <row r="24" ht="15.5" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>SEGMENT LAND &amp; HOUSING COST</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="38" t="inlineStr">
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="38" t="inlineStr">
         <is>
           <t>Northern</t>
         </is>
       </c>
-      <c r="C23" s="41" t="n">
+      <c r="C25" s="41" t="n">
         <v>1228949</v>
       </c>
-      <c r="D23" s="41" t="n">
+      <c r="D25" s="41" t="n">
         <v>1480326</v>
       </c>
-      <c r="E23" s="41" t="n">
+      <c r="E25" s="41" t="n">
         <v>1475438</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="38" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>Southern</t>
         </is>
       </c>
-      <c r="C24" s="41" t="n">
+      <c r="C26" s="41" t="n">
         <v>1785624</v>
       </c>
-      <c r="D24" s="41" t="n">
+      <c r="D26" s="41" t="n">
         <v>1825455</v>
       </c>
-      <c r="E24" s="41" t="n">
+      <c r="E26" s="41" t="n">
         <v>1925144</v>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="46" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  of which: inventory write-offs — Northern</t>
         </is>
       </c>
-      <c r="C25" s="41" t="n">
+      <c r="C27" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="41" t="n">
+      <c r="D27" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="41" t="n">
+      <c r="E27" s="41" t="n">
         <v>6700</v>
       </c>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>2025 total valuation adjustments $47.7m.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="46" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="46" t="inlineStr">
         <is>
           <t xml:space="preserve">  of which: inventory write-offs — Southern</t>
         </is>
       </c>
-      <c r="C26" s="41" t="n">
+      <c r="C28" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="41" t="n">
+      <c r="D28" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="41" t="n">
+      <c r="E28" s="41" t="n">
         <v>41000</v>
       </c>
     </row>
-    <row r="27" ht="6" customHeight="1"/>
-    <row r="28" ht="15.5" customHeight="1">
-      <c r="B28" s="3" t="inlineStr">
+    <row r="29" ht="6" customHeight="1"/>
+    <row r="30" ht="15.5" customHeight="1">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>SEGMENT OPERATING INCOME</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="38" t="inlineStr">
-        <is>
-          <t>Northern homebuilding</t>
-        </is>
-      </c>
-      <c r="C29" s="41" t="n">
-        <v>176320</v>
-      </c>
-      <c r="D29" s="41" t="n">
-        <v>281099</v>
-      </c>
-      <c r="E29" s="41" t="n">
-        <v>278056</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="38" t="inlineStr">
-        <is>
-          <t>Southern homebuilding</t>
-        </is>
-      </c>
-      <c r="C30" s="41" t="n">
-        <v>440168</v>
-      </c>
-      <c r="D30" s="41" t="n">
-        <v>450598</v>
-      </c>
-      <c r="E30" s="41" t="n">
-        <v>249969</v>
-      </c>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="38" t="inlineStr">
         <is>
-          <t>Financial services</t>
+          <t>Northern homebuilding</t>
         </is>
       </c>
       <c r="C31" s="41" t="n">
-        <v>48714</v>
+        <v>176320</v>
       </c>
       <c r="D31" s="41" t="n">
-        <v>63380</v>
+        <v>281099</v>
       </c>
       <c r="E31" s="41" t="n">
-        <v>68160</v>
+        <v>278056</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="38" t="inlineStr">
         <is>
+          <t>Southern homebuilding</t>
+        </is>
+      </c>
+      <c r="C32" s="41" t="n">
+        <v>440168</v>
+      </c>
+      <c r="D32" s="41" t="n">
+        <v>450598</v>
+      </c>
+      <c r="E32" s="41" t="n">
+        <v>249969</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="38" t="inlineStr">
+        <is>
+          <t>Financial services</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="n">
+        <v>48714</v>
+      </c>
+      <c r="D33" s="41" t="n">
+        <v>63380</v>
+      </c>
+      <c r="E33" s="41" t="n">
+        <v>68160</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="38" t="inlineStr">
+        <is>
           <t>Corporate / unallocated</t>
         </is>
       </c>
-      <c r="C32" s="13">
-        <f>Historicals!C33-C29-C30-C31</f>
-        <v/>
-      </c>
-      <c r="D32" s="13">
-        <f>Historicals!D33-D29-D30-D31</f>
-        <v/>
-      </c>
-      <c r="E32" s="13">
-        <f>Historicals!E33-E29-E30-E31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="44" t="inlineStr">
+      <c r="C34" s="13">
+        <f>Historicals!C35-C31-C32-C33</f>
+        <v/>
+      </c>
+      <c r="D34" s="13">
+        <f>Historicals!D35-D31-D32-D33</f>
+        <v/>
+      </c>
+      <c r="E34" s="13">
+        <f>Historicals!E35-E31-E32-E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="44" t="inlineStr">
         <is>
           <t>Total operating income</t>
         </is>
       </c>
-      <c r="C33" s="47" t="n">
+      <c r="C35" s="47" t="n">
         <v>587222</v>
       </c>
-      <c r="D33" s="47" t="n">
+      <c r="D35" s="47" t="n">
         <v>706094</v>
       </c>
-      <c r="E33" s="47" t="n">
+      <c r="E35" s="47" t="n">
         <v>506553</v>
       </c>
     </row>
-    <row r="34" ht="6" customHeight="1"/>
-    <row r="35" ht="15.5" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
+    <row r="36" ht="6" customHeight="1"/>
+    <row r="37" ht="15.5" customHeight="1">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>SEGMENT SELLING AND G&amp;A</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
-      <c r="J35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="38" t="inlineStr">
-        <is>
-          <t>Selling — Northern</t>
-        </is>
-      </c>
-      <c r="C36" s="41" t="n">
-        <v>81847</v>
-      </c>
-      <c r="D36" s="41" t="n">
-        <v>95680</v>
-      </c>
-      <c r="E36" s="41" t="n">
-        <v>95860</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="38" t="inlineStr">
-        <is>
-          <t>Selling — Southern</t>
-        </is>
-      </c>
-      <c r="C37" s="41" t="n">
-        <v>124860</v>
-      </c>
-      <c r="D37" s="41" t="n">
-        <v>136198</v>
-      </c>
-      <c r="E37" s="41" t="n">
-        <v>149457</v>
-      </c>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="B38" s="38" t="inlineStr">
         <is>
-          <t>G&amp;A — Northern</t>
+          <t>Selling — Northern</t>
         </is>
       </c>
       <c r="C38" s="41" t="n">
-        <v>36827</v>
+        <v>81847</v>
       </c>
       <c r="D38" s="41" t="n">
-        <v>42908</v>
+        <v>95680</v>
       </c>
       <c r="E38" s="41" t="n">
-        <v>41103</v>
+        <v>95860</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="38" t="inlineStr">
         <is>
-          <t>G&amp;A — Southern</t>
+          <t>Selling — Southern</t>
         </is>
       </c>
       <c r="C39" s="41" t="n">
-        <v>65078</v>
+        <v>124860</v>
       </c>
       <c r="D39" s="41" t="n">
-        <v>76200</v>
+        <v>136198</v>
       </c>
       <c r="E39" s="41" t="n">
-        <v>77291</v>
+        <v>149457</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="38" t="inlineStr">
         <is>
+          <t>G&amp;A — Northern</t>
+        </is>
+      </c>
+      <c r="C40" s="41" t="n">
+        <v>36827</v>
+      </c>
+      <c r="D40" s="41" t="n">
+        <v>42908</v>
+      </c>
+      <c r="E40" s="41" t="n">
+        <v>41103</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="38" t="inlineStr">
+        <is>
+          <t>G&amp;A — Southern</t>
+        </is>
+      </c>
+      <c r="C41" s="41" t="n">
+        <v>65078</v>
+      </c>
+      <c r="D41" s="41" t="n">
+        <v>76200</v>
+      </c>
+      <c r="E41" s="41" t="n">
+        <v>77291</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="38" t="inlineStr">
+        <is>
           <t>G&amp;A — Financial services</t>
         </is>
       </c>
-      <c r="C40" s="41" t="n">
+      <c r="C42" s="41" t="n">
         <v>45115</v>
       </c>
-      <c r="D40" s="41" t="n">
+      <c r="D42" s="41" t="n">
         <v>52826</v>
       </c>
-      <c r="E40" s="41" t="n">
+      <c r="E42" s="41" t="n">
         <v>57303</v>
       </c>
     </row>
-    <row r="41" ht="6" customHeight="1"/>
-    <row r="42" ht="15.5" customHeight="1">
-      <c r="B42" s="3" t="inlineStr">
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="15.5" customHeight="1">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>CONSOLIDATED INCOME STATEMENT   [FY2025 10-K; XBRL companyfacts CIK 0000799292]</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="n"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="38" t="inlineStr">
-        <is>
-          <t>Land and housing costs</t>
-        </is>
-      </c>
-      <c r="C43" s="41" t="n">
-        <v>3014573</v>
-      </c>
-      <c r="D43" s="41" t="n">
-        <v>3305781</v>
-      </c>
-      <c r="E43" s="41" t="n">
-        <v>3400582</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="38" t="inlineStr">
-        <is>
-          <t>Income before income taxes</t>
-        </is>
-      </c>
-      <c r="C44" s="41" t="n">
-        <v>607277</v>
-      </c>
-      <c r="D44" s="41" t="n">
-        <v>733608</v>
-      </c>
-      <c r="E44" s="41" t="n">
-        <v>526588</v>
-      </c>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="38" t="inlineStr">
         <is>
-          <t>Provision for income taxes</t>
+          <t>Land and housing costs</t>
         </is>
       </c>
       <c r="C45" s="41" t="n">
-        <v>141912</v>
+        <v>3014573</v>
       </c>
       <c r="D45" s="41" t="n">
-        <v>169883</v>
+        <v>3305781</v>
       </c>
       <c r="E45" s="41" t="n">
-        <v>123647</v>
+        <v>3400582</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="38" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t>Income before income taxes</t>
         </is>
       </c>
       <c r="C46" s="41" t="n">
-        <v>465365</v>
+        <v>607277</v>
       </c>
       <c r="D46" s="41" t="n">
-        <v>563725</v>
+        <v>733608</v>
       </c>
       <c r="E46" s="41" t="n">
-        <v>402941</v>
+        <v>526588</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="38" t="inlineStr">
         <is>
-          <t>Diluted EPS ($)</t>
-        </is>
-      </c>
-      <c r="C47" s="40" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="D47" s="40" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="E47" s="40" t="n">
-        <v>14.74</v>
+          <t>Provision for income taxes</t>
+        </is>
+      </c>
+      <c r="C47" s="41" t="n">
+        <v>141912</v>
+      </c>
+      <c r="D47" s="41" t="n">
+        <v>169883</v>
+      </c>
+      <c r="E47" s="41" t="n">
+        <v>123647</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="38" t="inlineStr">
         <is>
-          <t>Diluted weighted-average shares (000)</t>
+          <t>Net income</t>
         </is>
       </c>
       <c r="C48" s="41" t="n">
-        <v>28716</v>
+        <v>465365</v>
       </c>
       <c r="D48" s="41" t="n">
-        <v>28600</v>
+        <v>563725</v>
       </c>
       <c r="E48" s="41" t="n">
-        <v>27338</v>
+        <v>402941</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="38" t="inlineStr">
         <is>
+          <t>Diluted EPS ($)</t>
+        </is>
+      </c>
+      <c r="C49" s="40" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="D49" s="40" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="E49" s="40" t="n">
+        <v>14.74</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="38" t="inlineStr">
+        <is>
+          <t>Diluted weighted-average shares (000)</t>
+        </is>
+      </c>
+      <c r="C50" s="41" t="n">
+        <v>28716</v>
+      </c>
+      <c r="D50" s="41" t="n">
+        <v>28600</v>
+      </c>
+      <c r="E50" s="41" t="n">
+        <v>27338</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="38" t="inlineStr">
+        <is>
           <t>Shares outstanding, year end (000)</t>
         </is>
       </c>
-      <c r="C49" s="41" t="n">
+      <c r="C51" s="41" t="n">
         <v>27600</v>
       </c>
-      <c r="D49" s="41" t="n">
+      <c r="D51" s="41" t="n">
         <v>27060</v>
       </c>
-      <c r="E49" s="41" t="n">
+      <c r="E51" s="41" t="n">
         <v>25763</v>
       </c>
     </row>
-    <row r="50" ht="6" customHeight="1"/>
-    <row r="51" ht="15.5" customHeight="1">
-      <c r="B51" s="3" t="inlineStr">
+    <row r="52" ht="6" customHeight="1"/>
+    <row r="53" ht="15.5" customHeight="1">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>CONSOLIDATED BALANCE SHEET / CASH FLOW</t>
         </is>
       </c>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n"/>
-      <c r="G51" s="3" t="n"/>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
-      <c r="J51" s="3" t="n"/>
-    </row>
-    <row r="52">
-      <c r="B52" s="38" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="C52" s="41" t="n">
-        <v>733000</v>
-      </c>
-      <c r="D52" s="41" t="n">
-        <v>821600</v>
-      </c>
-      <c r="E52" s="41" t="n">
-        <v>689200</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="38" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="C53" s="41" t="n">
-        <v>2797151</v>
-      </c>
-      <c r="D53" s="41" t="n">
-        <v>3091862</v>
-      </c>
-      <c r="E53" s="41" t="n">
-        <v>3383941</v>
-      </c>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+      <c r="I53" s="3" t="n"/>
+      <c r="J53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="B54" s="38" t="inlineStr">
         <is>
-          <t>Total assets</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="C54" s="41" t="n">
-        <v>4022440</v>
+        <v>733000</v>
       </c>
       <c r="D54" s="41" t="n">
-        <v>4549796</v>
+        <v>821600</v>
       </c>
       <c r="E54" s="41" t="n">
-        <v>4777125</v>
+        <v>689200</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="38" t="inlineStr">
         <is>
-          <t>Homebuilding debt</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="C55" s="41" t="n">
-        <v>693744</v>
+        <v>2797151</v>
       </c>
       <c r="D55" s="41" t="n">
-        <v>695022</v>
+        <v>3091862</v>
       </c>
       <c r="E55" s="41" t="n">
-        <v>696300</v>
+        <v>3383941</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="38" t="inlineStr">
         <is>
-          <t>Financial services debt</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="C56" s="41" t="n">
-        <v>165844</v>
+        <v>4022440</v>
       </c>
       <c r="D56" s="41" t="n">
-        <v>286159</v>
+        <v>4549796</v>
       </c>
       <c r="E56" s="41" t="n">
-        <v>276856</v>
+        <v>4777125</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="38" t="inlineStr">
         <is>
-          <t>Shareholders' equity</t>
+          <t>Homebuilding debt</t>
         </is>
       </c>
       <c r="C57" s="41" t="n">
-        <v>2516939</v>
+        <v>693744</v>
       </c>
       <c r="D57" s="41" t="n">
-        <v>2939677</v>
+        <v>695022</v>
       </c>
       <c r="E57" s="41" t="n">
-        <v>3166190</v>
+        <v>696300</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="38" t="inlineStr">
         <is>
-          <t>Cash from operating activities</t>
+          <t>Financial services debt</t>
         </is>
       </c>
       <c r="C58" s="41" t="n">
-        <v>552131</v>
+        <v>165844</v>
       </c>
       <c r="D58" s="41" t="n">
-        <v>179736</v>
+        <v>286159</v>
       </c>
       <c r="E58" s="41" t="n">
-        <v>137349</v>
+        <v>276856</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="38" t="inlineStr">
         <is>
-          <t>Depreciation &amp; amortisation</t>
+          <t>Shareholders' equity</t>
         </is>
       </c>
       <c r="C59" s="41" t="n">
-        <v>15791</v>
+        <v>2516939</v>
       </c>
       <c r="D59" s="41" t="n">
-        <v>17386</v>
+        <v>2939677</v>
       </c>
       <c r="E59" s="41" t="n">
-        <v>18898</v>
+        <v>3166190</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="38" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Cash from operating activities</t>
         </is>
       </c>
       <c r="C60" s="41" t="n">
-        <v>11370</v>
+        <v>552131</v>
       </c>
       <c r="D60" s="41" t="n">
-        <v>14564</v>
+        <v>179736</v>
       </c>
       <c r="E60" s="41" t="n">
-        <v>16998</v>
+        <v>137349</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="38" t="inlineStr">
         <is>
-          <t>Capital expenditure</t>
+          <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
       <c r="C61" s="41" t="n">
-        <v>5769</v>
+        <v>15791</v>
       </c>
       <c r="D61" s="41" t="n">
-        <v>8417</v>
+        <v>17386</v>
       </c>
       <c r="E61" s="41" t="n">
-        <v>9609</v>
+        <v>18898</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="38" t="inlineStr">
         <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="C62" s="41" t="n">
+        <v>11370</v>
+      </c>
+      <c r="D62" s="41" t="n">
+        <v>14564</v>
+      </c>
+      <c r="E62" s="41" t="n">
+        <v>16998</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="38" t="inlineStr">
+        <is>
+          <t>Capital expenditure</t>
+        </is>
+      </c>
+      <c r="C63" s="41" t="n">
+        <v>5769</v>
+      </c>
+      <c r="D63" s="41" t="n">
+        <v>8417</v>
+      </c>
+      <c r="E63" s="41" t="n">
+        <v>9609</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="38" t="inlineStr">
+        <is>
           <t>Share repurchases</t>
         </is>
       </c>
-      <c r="C62" s="41" t="n">
+      <c r="C64" s="41" t="n">
         <v>65344</v>
       </c>
-      <c r="D62" s="41" t="n">
+      <c r="D64" s="41" t="n">
         <v>176953</v>
       </c>
-      <c r="E62" s="41" t="n">
+      <c r="E64" s="41" t="n">
         <v>202033</v>
       </c>
     </row>
-    <row r="63" ht="6" customHeight="1"/>
-    <row r="64" ht="15.5" customHeight="1">
-      <c r="B64" s="3" t="inlineStr">
+    <row r="65" ht="6" customHeight="1"/>
+    <row r="66" ht="15.5" customHeight="1">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>DERIVED DIAGNOSTICS  —  the analytical core of the note</t>
         </is>
       </c>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n"/>
-      <c r="G64" s="3" t="n"/>
-      <c r="H64" s="3" t="n"/>
-      <c r="I64" s="3" t="n"/>
-      <c r="J64" s="3" t="n"/>
-    </row>
-    <row r="65">
-      <c r="B65" s="38" t="inlineStr">
-        <is>
-          <t>Net ASP — Northern ($000)</t>
-        </is>
-      </c>
-      <c r="C65" s="48">
-        <f>C17/C8</f>
-        <v/>
-      </c>
-      <c r="D65" s="48">
-        <f>D17/D8</f>
-        <v/>
-      </c>
-      <c r="E65" s="48">
-        <f>E17/E8</f>
-        <v/>
-      </c>
-      <c r="L65" s="9" t="inlineStr">
-        <is>
-          <t>Segment revenue per home delivered. Northern price is RISING.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="38" t="inlineStr">
-        <is>
-          <t>Net ASP — Southern ($000)</t>
-        </is>
-      </c>
-      <c r="C66" s="48">
-        <f>C18/C9</f>
-        <v/>
-      </c>
-      <c r="D66" s="48">
-        <f>D18/D9</f>
-        <v/>
-      </c>
-      <c r="E66" s="48">
-        <f>E18/E9</f>
-        <v/>
-      </c>
-      <c r="L66" s="9" t="inlineStr">
-        <is>
-          <t>Southern price is FALLING: $488.7k → $461.5k, −5.6% over two years.</t>
-        </is>
-      </c>
+      <c r="C66" s="3" t="n"/>
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+      <c r="I66" s="3" t="n"/>
+      <c r="J66" s="3" t="n"/>
     </row>
     <row r="67">
       <c r="B67" s="38" t="inlineStr">
         <is>
-          <t>Cost per home ex-charges — Northern ($000)</t>
+          <t>Net ASP — Northern ($000)</t>
         </is>
       </c>
       <c r="C67" s="48">
-        <f>(C23-C25)/C8</f>
+        <f>(C17-C21*(1-Assumptions!$C$38/100))/C8</f>
         <v/>
       </c>
       <c r="D67" s="48">
-        <f>(D23-D25)/D8</f>
+        <f>(D17-D21*(1-Assumptions!$C$38/100))/D8</f>
         <v/>
       </c>
       <c r="E67" s="48">
-        <f>(E23-E25)/E8</f>
-        <v/>
+        <f>(E17-E21*(1-Assumptions!$C$38/100))/E8</f>
+        <v/>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>Housing revenue per home delivered, land sales stripped out. Northern price is RISING.</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="38" t="inlineStr">
         <is>
-          <t>Cost per home ex-charges — Southern ($000)</t>
+          <t>Net ASP — Southern ($000)</t>
         </is>
       </c>
       <c r="C68" s="48">
-        <f>(C24-C26)/C9</f>
+        <f>(C18-C21*Assumptions!$C$38/100)/C9</f>
         <v/>
       </c>
       <c r="D68" s="48">
-        <f>(D24-D26)/D9</f>
+        <f>(D18-D21*Assumptions!$C$38/100)/D9</f>
         <v/>
       </c>
       <c r="E68" s="48">
-        <f>(E24-E26)/E9</f>
+        <f>(E18-E21*Assumptions!$C$38/100)/E9</f>
         <v/>
       </c>
       <c r="L68" s="9" t="inlineStr">
         <is>
-          <t>Up just 2.4% over two years. Cost is not the problem — price is.</t>
+          <t>Southern price is FALLING. Land sale revenue is excluded so this is a home price; the company-wide equivalent ties to the disclosed average closing price of $483 / $483 / $479.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="38" t="inlineStr">
         <is>
-          <t>Gross margin — Northern (%)</t>
-        </is>
-      </c>
-      <c r="C69" s="16">
-        <f>1-C23/C17</f>
-        <v/>
-      </c>
-      <c r="D69" s="16">
-        <f>1-D23/D17</f>
-        <v/>
-      </c>
-      <c r="E69" s="16">
-        <f>1-E23/E17</f>
+          <t>Cost per home ex-charges — Northern ($000)</t>
+        </is>
+      </c>
+      <c r="C69" s="48">
+        <f>(C25-C27-(C21-C22)*(1-Assumptions!$C$38/100))/C8</f>
+        <v/>
+      </c>
+      <c r="D69" s="48">
+        <f>(D25-D27-(D21-D22)*(1-Assumptions!$C$38/100))/D8</f>
+        <v/>
+      </c>
+      <c r="E69" s="48">
+        <f>(E25-E27-(E21-E22)*(1-Assumptions!$C$38/100))/E8</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="38" t="inlineStr">
         <is>
-          <t>Gross margin — Southern (%)</t>
-        </is>
-      </c>
-      <c r="C70" s="16">
-        <f>1-C24/C18</f>
-        <v/>
-      </c>
-      <c r="D70" s="16">
-        <f>1-D24/D18</f>
-        <v/>
-      </c>
-      <c r="E70" s="16">
-        <f>1-E24/E18</f>
+          <t>Cost per home ex-charges — Southern ($000)</t>
+        </is>
+      </c>
+      <c r="C70" s="48">
+        <f>(C26-C28-(C21-C22)*Assumptions!$C$38/100)/C9</f>
+        <v/>
+      </c>
+      <c r="D70" s="48">
+        <f>(D26-D28-(D21-D22)*Assumptions!$C$38/100)/D9</f>
+        <v/>
+      </c>
+      <c r="E70" s="48">
+        <f>(E26-E28-(E21-E22)*Assumptions!$C$38/100)/E9</f>
         <v/>
       </c>
       <c r="L70" s="9" t="inlineStr">
         <is>
-          <t>26.1% → 26.6% → 19.8%. A 680bp collapse in one year.</t>
+          <t>Cost is not the problem — price is.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="38" t="inlineStr">
         <is>
-          <t>Gross margin — homebuilding only (%)</t>
+          <t>Gross margin — Northern (%)</t>
         </is>
       </c>
       <c r="C71" s="16">
-        <f>1-C43/(C17+C18)</f>
+        <f>1-C25/C17</f>
         <v/>
       </c>
       <c r="D71" s="16">
-        <f>1-D43/(D17+D18)</f>
+        <f>1-D25/D17</f>
         <v/>
       </c>
       <c r="E71" s="16">
-        <f>1-E43/(E17+E18)</f>
+        <f>1-E25/E17</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="49" t="inlineStr">
-        <is>
-          <t>Gross margin — as reported (%)</t>
-        </is>
-      </c>
-      <c r="C72" s="34">
-        <f>1-C43/C20</f>
-        <v/>
-      </c>
-      <c r="D72" s="34">
-        <f>1-D43/D20</f>
-        <v/>
-      </c>
-      <c r="E72" s="34">
-        <f>1-E43/E20</f>
+      <c r="B72" s="38" t="inlineStr">
+        <is>
+          <t>Gross margin — Southern (%)</t>
+        </is>
+      </c>
+      <c r="C72" s="16">
+        <f>1-C26/C18</f>
+        <v/>
+      </c>
+      <c r="D72" s="16">
+        <f>1-D26/D18</f>
+        <v/>
+      </c>
+      <c r="E72" s="16">
+        <f>1-E26/E18</f>
         <v/>
       </c>
       <c r="L72" s="9" t="inlineStr">
         <is>
-          <t>NOTE: MHO reports gross margin on TOTAL revenue, which includes zero-cost financial services revenue. That flatters the headline by ~200bp. Use the homebuilding line above for like-for-like work.</t>
+          <t>26.1% → 26.6% → 19.8%. A 680bp collapse in one year.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="38" t="inlineStr">
         <is>
-          <t>Operating margin — Northern (%)</t>
+          <t>Gross margin — homebuilding only (%)</t>
         </is>
       </c>
       <c r="C73" s="16">
-        <f>C29/C17</f>
+        <f>1-C45/(C17+C18)</f>
         <v/>
       </c>
       <c r="D73" s="16">
-        <f>D29/D17</f>
+        <f>1-D45/(D17+D18)</f>
         <v/>
       </c>
       <c r="E73" s="16">
-        <f>E29/E17</f>
+        <f>1-E45/(E17+E18)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="49" t="inlineStr">
         <is>
-          <t>Operating margin — Southern (%)</t>
+          <t>Gross margin — as reported (%)</t>
         </is>
       </c>
       <c r="C74" s="34">
-        <f>C30/C18</f>
+        <f>1-C45/C20</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>D30/D18</f>
+        <f>1-D45/D20</f>
         <v/>
       </c>
       <c r="E74" s="34">
-        <f>E30/E18</f>
+        <f>1-E45/E20</f>
         <v/>
       </c>
       <c r="L74" s="9" t="inlineStr">
         <is>
-          <t>18.2% → 18.1% → 10.4%, while Northern went 11.6% → 14.8% → 14.7%.</t>
+          <t>NOTE: MHO reports gross margin on TOTAL revenue, which includes zero-cost financial services revenue. That flatters the headline by ~200bp. Use the homebuilding line above for like-for-like work.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="38" t="inlineStr">
         <is>
-          <t>Southern share of deliveries (%)</t>
+          <t>Operating margin — Northern (%)</t>
         </is>
       </c>
       <c r="C75" s="16">
-        <f>C9/C10</f>
+        <f>C31/C17</f>
         <v/>
       </c>
       <c r="D75" s="16">
-        <f>D9/D10</f>
+        <f>D31/D17</f>
         <v/>
       </c>
       <c r="E75" s="16">
-        <f>E9/E10</f>
+        <f>E31/E17</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="49" t="inlineStr">
         <is>
-          <t>Southern share of segment operating income (%)</t>
+          <t>Operating margin — Southern (%)</t>
         </is>
       </c>
       <c r="C76" s="34">
-        <f>C30/(C29+C30)</f>
+        <f>C32/C18</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>D30/(D29+D30)</f>
+        <f>D32/D18</f>
         <v/>
       </c>
       <c r="E76" s="34">
-        <f>E30/(E29+E30)</f>
+        <f>E32/E18</f>
         <v/>
       </c>
       <c r="L76" s="9" t="inlineStr">
         <is>
-          <t>71% → 47%. The growth region stopped carrying the P&amp;L.</t>
+          <t>18.2% → 18.1% → 10.4%, while Northern went 11.6% → 14.8% → 14.7%.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="38" t="inlineStr">
         <is>
+          <t>Southern share of deliveries (%)</t>
+        </is>
+      </c>
+      <c r="C77" s="16">
+        <f>C9/C10</f>
+        <v/>
+      </c>
+      <c r="D77" s="16">
+        <f>D9/D10</f>
+        <v/>
+      </c>
+      <c r="E77" s="16">
+        <f>E9/E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="49" t="inlineStr">
+        <is>
+          <t>Southern share of segment operating income (%)</t>
+        </is>
+      </c>
+      <c r="C78" s="34">
+        <f>C32/(C31+C32)</f>
+        <v/>
+      </c>
+      <c r="D78" s="34">
+        <f>D32/(D31+D32)</f>
+        <v/>
+      </c>
+      <c r="E78" s="34">
+        <f>E32/(E31+E32)</f>
+        <v/>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>71% → 47%. The growth region stopped carrying the P&amp;L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="38" t="inlineStr">
+        <is>
           <t>Return on equity (%)</t>
         </is>
       </c>
-      <c r="C77" s="16">
-        <f>C46/C57</f>
-        <v/>
-      </c>
-      <c r="D77" s="16">
-        <f>D46/D57</f>
-        <v/>
-      </c>
-      <c r="E77" s="16">
-        <f>E46/E57</f>
-        <v/>
-      </c>
-      <c r="L77" s="9" t="inlineStr">
+      <c r="C79" s="16">
+        <f>C48/C59</f>
+        <v/>
+      </c>
+      <c r="D79" s="16">
+        <f>D48/D59</f>
+        <v/>
+      </c>
+      <c r="E79" s="16">
+        <f>E48/E59</f>
+        <v/>
+      </c>
+      <c r="L79" s="9" t="inlineStr">
         <is>
           <t>18.5% → 19.2% → 12.7%.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="38" t="inlineStr">
+    <row r="80">
+      <c r="B80" s="38" t="inlineStr">
         <is>
           <t>Book value per share ($)</t>
         </is>
       </c>
-      <c r="C78" s="50">
-        <f>C57/C49</f>
-        <v/>
-      </c>
-      <c r="D78" s="50">
-        <f>D57/D49</f>
-        <v/>
-      </c>
-      <c r="E78" s="50">
-        <f>E57/E49</f>
+      <c r="C80" s="50">
+        <f>C59/C51</f>
+        <v/>
+      </c>
+      <c r="D80" s="50">
+        <f>D59/D51</f>
+        <v/>
+      </c>
+      <c r="E80" s="50">
+        <f>E59/E51</f>
         <v/>
       </c>
     </row>
@@ -5881,23 +5981,23 @@
         <v/>
       </c>
       <c r="F8" s="13">
-        <f>E8*(1+Assumptions!F20/100)</f>
+        <f>E8*(1+Assumptions!F22/100)</f>
         <v/>
       </c>
       <c r="G8" s="13">
-        <f>F8*(1+Assumptions!G20/100)</f>
+        <f>F8*(1+Assumptions!G22/100)</f>
         <v/>
       </c>
       <c r="H8" s="13">
-        <f>G8*(1+Assumptions!H20/100)</f>
+        <f>G8*(1+Assumptions!H22/100)</f>
         <v/>
       </c>
       <c r="I8" s="13">
-        <f>H8*(1+Assumptions!I20/100)</f>
+        <f>H8*(1+Assumptions!I22/100)</f>
         <v/>
       </c>
       <c r="J8" s="13">
-        <f>I8*(1+Assumptions!J20/100)</f>
+        <f>I8*(1+Assumptions!J22/100)</f>
         <v/>
       </c>
     </row>
@@ -5920,23 +6020,23 @@
         <v/>
       </c>
       <c r="F9" s="48">
-        <f>E9*(1+Assumptions!F22/100)</f>
+        <f>E9*(1+Assumptions!F24/100)</f>
         <v/>
       </c>
       <c r="G9" s="48">
-        <f>F9*(1+Assumptions!G22/100)</f>
+        <f>F9*(1+Assumptions!G24/100)</f>
         <v/>
       </c>
       <c r="H9" s="48">
-        <f>G9*(1+Assumptions!H22/100)</f>
+        <f>G9*(1+Assumptions!H24/100)</f>
         <v/>
       </c>
       <c r="I9" s="48">
-        <f>H9*(1+Assumptions!I22/100)</f>
+        <f>H9*(1+Assumptions!I24/100)</f>
         <v/>
       </c>
       <c r="J9" s="48">
-        <f>I9*(1+Assumptions!J22/100)</f>
+        <f>I9*(1+Assumptions!J24/100)</f>
         <v/>
       </c>
     </row>
@@ -5947,35 +6047,35 @@
         </is>
       </c>
       <c r="C10" s="52">
-        <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!C8-Assumptions!$C$9)+Assumptions!C14</f>
+        <f>Assumptions!$C$14+Assumptions!$C$15*MAX(0,Assumptions!C8-Assumptions!$C$9)+Assumptions!C16</f>
         <v/>
       </c>
       <c r="D10" s="52">
-        <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!D8-Assumptions!$C$9)+Assumptions!D14</f>
+        <f>Assumptions!$C$14+Assumptions!$C$15*MAX(0,Assumptions!D8-Assumptions!$C$9)+Assumptions!D16</f>
         <v/>
       </c>
       <c r="E10" s="52">
-        <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!E8-Assumptions!$C$9)+Assumptions!E14</f>
+        <f>Assumptions!$C$14+Assumptions!$C$15*MAX(0,Assumptions!E8-Assumptions!$C$9)+Assumptions!E16</f>
         <v/>
       </c>
       <c r="F10" s="52">
-        <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!F8-Assumptions!$C$9)+Assumptions!F14</f>
+        <f>Assumptions!$C$14+Assumptions!$C$15*MAX(0,Assumptions!F8-Assumptions!$C$9)+Assumptions!F16</f>
         <v/>
       </c>
       <c r="G10" s="52">
-        <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!G8-Assumptions!$C$9)+Assumptions!G14</f>
+        <f>Assumptions!$C$14+Assumptions!$C$15*MAX(0,Assumptions!G8-Assumptions!$C$9)+Assumptions!G16</f>
         <v/>
       </c>
       <c r="H10" s="52">
-        <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!H8-Assumptions!$C$9)+Assumptions!H14</f>
+        <f>Assumptions!$C$14+Assumptions!$C$15*MAX(0,Assumptions!H8-Assumptions!$C$9)+Assumptions!H16</f>
         <v/>
       </c>
       <c r="I10" s="52">
-        <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!I8-Assumptions!$C$9)+Assumptions!I14</f>
+        <f>Assumptions!$C$14+Assumptions!$C$15*MAX(0,Assumptions!I8-Assumptions!$C$9)+Assumptions!I16</f>
         <v/>
       </c>
       <c r="J10" s="52">
-        <f>Assumptions!$C$12+Assumptions!$C$13*MAX(0,Assumptions!J8-Assumptions!$C$9)+Assumptions!J14</f>
+        <f>Assumptions!$C$14+Assumptions!$C$15*MAX(0,Assumptions!J8-Assumptions!$C$9)+Assumptions!J16</f>
         <v/>
       </c>
       <c r="L10" s="9" t="inlineStr">
@@ -5991,15 +6091,15 @@
         </is>
       </c>
       <c r="C11" s="53">
-        <f>Historicals!C17/C8</f>
+        <f>(Historicals!C17-Historicals!C21*(1-Assumptions!$C$38/100))/C8</f>
         <v/>
       </c>
       <c r="D11" s="53">
-        <f>Historicals!D17/D8</f>
+        <f>(Historicals!D17-Historicals!D21*(1-Assumptions!$C$38/100))/D8</f>
         <v/>
       </c>
       <c r="E11" s="53">
-        <f>Historicals!E17/E8</f>
+        <f>(Historicals!E17-Historicals!E21*(1-Assumptions!$C$38/100))/E8</f>
         <v/>
       </c>
       <c r="F11" s="54">
@@ -6030,35 +6130,35 @@
         </is>
       </c>
       <c r="C12" s="55">
-        <f>(Historicals!C23-Historicals!C25)/C8</f>
+        <f>(Historicals!C25-Historicals!C27-(Historicals!C21-Historicals!C22)*(1-Assumptions!$C$38/100))/C8</f>
         <v/>
       </c>
       <c r="D12" s="55">
-        <f>(Historicals!D23-Historicals!D25)/D8</f>
+        <f>(Historicals!D25-Historicals!D27-(Historicals!D21-Historicals!D22)*(1-Assumptions!$C$38/100))/D8</f>
         <v/>
       </c>
       <c r="E12" s="55">
-        <f>(Historicals!E23-Historicals!E25)/E8</f>
+        <f>(Historicals!E25-Historicals!E27-(Historicals!E21-Historicals!E22)*(1-Assumptions!$C$38/100))/E8</f>
         <v/>
       </c>
       <c r="F12" s="48">
-        <f>E12*(1+Assumptions!F24/100)</f>
+        <f>E12*(1+Assumptions!F26/100)</f>
         <v/>
       </c>
       <c r="G12" s="48">
-        <f>F12*(1+Assumptions!G24/100)</f>
+        <f>F12*(1+Assumptions!G26/100)</f>
         <v/>
       </c>
       <c r="H12" s="48">
-        <f>G12*(1+Assumptions!H24/100)</f>
+        <f>G12*(1+Assumptions!H26/100)</f>
         <v/>
       </c>
       <c r="I12" s="48">
-        <f>H12*(1+Assumptions!I24/100)</f>
+        <f>H12*(1+Assumptions!I26/100)</f>
         <v/>
       </c>
       <c r="J12" s="48">
-        <f>I12*(1+Assumptions!J24/100)</f>
+        <f>I12*(1+Assumptions!J26/100)</f>
         <v/>
       </c>
     </row>
@@ -6214,23 +6314,23 @@
         <v/>
       </c>
       <c r="F18" s="13">
-        <f>E18*(1+Assumptions!F21/100)</f>
+        <f>E18*(1+Assumptions!F23/100)</f>
         <v/>
       </c>
       <c r="G18" s="13">
-        <f>F18*(1+Assumptions!G21/100)</f>
+        <f>F18*(1+Assumptions!G23/100)</f>
         <v/>
       </c>
       <c r="H18" s="13">
-        <f>G18*(1+Assumptions!H21/100)</f>
+        <f>G18*(1+Assumptions!H23/100)</f>
         <v/>
       </c>
       <c r="I18" s="13">
-        <f>H18*(1+Assumptions!I21/100)</f>
+        <f>H18*(1+Assumptions!I23/100)</f>
         <v/>
       </c>
       <c r="J18" s="13">
-        <f>I18*(1+Assumptions!J21/100)</f>
+        <f>I18*(1+Assumptions!J23/100)</f>
         <v/>
       </c>
     </row>
@@ -6253,23 +6353,23 @@
         <v/>
       </c>
       <c r="F19" s="48">
-        <f>E19*(1+Assumptions!F23/100)</f>
+        <f>E19*(1+Assumptions!F25/100)</f>
         <v/>
       </c>
       <c r="G19" s="48">
-        <f>F19*(1+Assumptions!G23/100)</f>
+        <f>F19*(1+Assumptions!G25/100)</f>
         <v/>
       </c>
       <c r="H19" s="48">
-        <f>G19*(1+Assumptions!H23/100)</f>
+        <f>G19*(1+Assumptions!H25/100)</f>
         <v/>
       </c>
       <c r="I19" s="48">
-        <f>H19*(1+Assumptions!I23/100)</f>
+        <f>H19*(1+Assumptions!I25/100)</f>
         <v/>
       </c>
       <c r="J19" s="48">
-        <f>I19*(1+Assumptions!J23/100)</f>
+        <f>I19*(1+Assumptions!J25/100)</f>
         <v/>
       </c>
     </row>
@@ -6280,40 +6380,40 @@
         </is>
       </c>
       <c r="C20" s="52">
-        <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!C8-Assumptions!$C$9)+Assumptions!C17</f>
+        <f>Assumptions!$C$17+Assumptions!$C$18*MAX(0,Assumptions!C8-Assumptions!$C$9)+Assumptions!C19</f>
         <v/>
       </c>
       <c r="D20" s="52">
-        <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!D8-Assumptions!$C$9)+Assumptions!D17</f>
+        <f>Assumptions!$C$17+Assumptions!$C$18*MAX(0,Assumptions!D8-Assumptions!$C$9)+Assumptions!D19</f>
         <v/>
       </c>
       <c r="E20" s="52">
-        <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!E8-Assumptions!$C$9)+Assumptions!E17</f>
+        <f>Assumptions!$C$17+Assumptions!$C$18*MAX(0,Assumptions!E8-Assumptions!$C$9)+Assumptions!E19</f>
         <v/>
       </c>
       <c r="F20" s="52">
-        <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!F8-Assumptions!$C$9)+Assumptions!F17</f>
+        <f>Assumptions!$C$17+Assumptions!$C$18*MAX(0,Assumptions!F8-Assumptions!$C$9)+Assumptions!F19</f>
         <v/>
       </c>
       <c r="G20" s="52">
-        <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!G8-Assumptions!$C$9)+Assumptions!G17</f>
+        <f>Assumptions!$C$17+Assumptions!$C$18*MAX(0,Assumptions!G8-Assumptions!$C$9)+Assumptions!G19</f>
         <v/>
       </c>
       <c r="H20" s="52">
-        <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!H8-Assumptions!$C$9)+Assumptions!H17</f>
+        <f>Assumptions!$C$17+Assumptions!$C$18*MAX(0,Assumptions!H8-Assumptions!$C$9)+Assumptions!H19</f>
         <v/>
       </c>
       <c r="I20" s="52">
-        <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!I8-Assumptions!$C$9)+Assumptions!I17</f>
+        <f>Assumptions!$C$17+Assumptions!$C$18*MAX(0,Assumptions!I8-Assumptions!$C$9)+Assumptions!I19</f>
         <v/>
       </c>
       <c r="J20" s="52">
-        <f>Assumptions!$C$15+Assumptions!$C$16*MAX(0,Assumptions!J8-Assumptions!$C$9)+Assumptions!J17</f>
+        <f>Assumptions!$C$17+Assumptions!$C$18*MAX(0,Assumptions!J8-Assumptions!$C$9)+Assumptions!J19</f>
         <v/>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>Base + rate slope + competition premium. In 2025 the rate term contributed 4.5pp and competition 3.6pp.</t>
+          <t>Base + rate slope + competition premium. In 2025 the rate term contributed 1.31pp and competition 2.04pp, on a base of 2.05pp.</t>
         </is>
       </c>
     </row>
@@ -6324,15 +6424,15 @@
         </is>
       </c>
       <c r="C21" s="53">
-        <f>Historicals!C18/C18</f>
+        <f>(Historicals!C18-Historicals!C21*Assumptions!$C$38/100)/C18</f>
         <v/>
       </c>
       <c r="D21" s="53">
-        <f>Historicals!D18/D18</f>
+        <f>(Historicals!D18-Historicals!D21*Assumptions!$C$38/100)/D18</f>
         <v/>
       </c>
       <c r="E21" s="53">
-        <f>Historicals!E18/E18</f>
+        <f>(Historicals!E18-Historicals!E21*Assumptions!$C$38/100)/E18</f>
         <v/>
       </c>
       <c r="F21" s="54">
@@ -6363,35 +6463,35 @@
         </is>
       </c>
       <c r="C22" s="55">
-        <f>(Historicals!C24-Historicals!C26)/C18</f>
+        <f>(Historicals!C26-Historicals!C28-(Historicals!C21-Historicals!C22)*Assumptions!$C$38/100)/C18</f>
         <v/>
       </c>
       <c r="D22" s="55">
-        <f>(Historicals!D24-Historicals!D26)/D18</f>
+        <f>(Historicals!D26-Historicals!D28-(Historicals!D21-Historicals!D22)*Assumptions!$C$38/100)/D18</f>
         <v/>
       </c>
       <c r="E22" s="55">
-        <f>(Historicals!E24-Historicals!E26)/E18</f>
+        <f>(Historicals!E26-Historicals!E28-(Historicals!E21-Historicals!E22)*Assumptions!$C$38/100)/E18</f>
         <v/>
       </c>
       <c r="F22" s="48">
-        <f>E22*(1+Assumptions!F25/100)</f>
+        <f>E22*(1+Assumptions!F27/100)</f>
         <v/>
       </c>
       <c r="G22" s="48">
-        <f>F22*(1+Assumptions!G25/100)</f>
+        <f>F22*(1+Assumptions!G27/100)</f>
         <v/>
       </c>
       <c r="H22" s="48">
-        <f>G22*(1+Assumptions!H25/100)</f>
+        <f>G22*(1+Assumptions!H27/100)</f>
         <v/>
       </c>
       <c r="I22" s="48">
-        <f>H22*(1+Assumptions!I25/100)</f>
+        <f>H22*(1+Assumptions!I27/100)</f>
         <v/>
       </c>
       <c r="J22" s="48">
-        <f>I22*(1+Assumptions!J25/100)</f>
+        <f>I22*(1+Assumptions!J27/100)</f>
         <v/>
       </c>
     </row>
@@ -6547,23 +6647,23 @@
         <v/>
       </c>
       <c r="F28" s="51">
-        <f>Assumptions!F28</f>
+        <f>Assumptions!F30</f>
         <v/>
       </c>
       <c r="G28" s="51">
-        <f>Assumptions!G28</f>
+        <f>Assumptions!G30</f>
         <v/>
       </c>
       <c r="H28" s="51">
-        <f>Assumptions!H28</f>
+        <f>Assumptions!H30</f>
         <v/>
       </c>
       <c r="I28" s="51">
-        <f>Assumptions!I28</f>
+        <f>Assumptions!I30</f>
         <v/>
       </c>
       <c r="J28" s="51">
-        <f>Assumptions!J28</f>
+        <f>Assumptions!J30</f>
         <v/>
       </c>
     </row>
@@ -6586,23 +6686,23 @@
         <v/>
       </c>
       <c r="F29" s="13">
-        <f>E29*(1+Assumptions!F29/100)</f>
+        <f>E29*(1+Assumptions!F31/100)</f>
         <v/>
       </c>
       <c r="G29" s="13">
-        <f>F29*(1+Assumptions!G29/100)</f>
+        <f>F29*(1+Assumptions!G31/100)</f>
         <v/>
       </c>
       <c r="H29" s="13">
-        <f>G29*(1+Assumptions!H29/100)</f>
+        <f>G29*(1+Assumptions!H31/100)</f>
         <v/>
       </c>
       <c r="I29" s="13">
-        <f>H29*(1+Assumptions!I29/100)</f>
+        <f>H29*(1+Assumptions!I31/100)</f>
         <v/>
       </c>
       <c r="J29" s="13">
-        <f>I29*(1+Assumptions!J29/100)</f>
+        <f>I29*(1+Assumptions!J31/100)</f>
         <v/>
       </c>
     </row>
@@ -6641,23 +6741,23 @@
         <v/>
       </c>
       <c r="F32" s="13">
-        <f>F15+F28*(1-Assumptions!$C$36/100)</f>
+        <f>F15+F28*(1-Assumptions!$C$38/100)</f>
         <v/>
       </c>
       <c r="G32" s="13">
-        <f>G15+G28*(1-Assumptions!$C$36/100)</f>
+        <f>G15+G28*(1-Assumptions!$C$38/100)</f>
         <v/>
       </c>
       <c r="H32" s="13">
-        <f>H15+H28*(1-Assumptions!$C$36/100)</f>
+        <f>H15+H28*(1-Assumptions!$C$38/100)</f>
         <v/>
       </c>
       <c r="I32" s="13">
-        <f>I15+I28*(1-Assumptions!$C$36/100)</f>
+        <f>I15+I28*(1-Assumptions!$C$38/100)</f>
         <v/>
       </c>
       <c r="J32" s="13">
-        <f>J15+J28*(1-Assumptions!$C$36/100)</f>
+        <f>J15+J28*(1-Assumptions!$C$38/100)</f>
         <v/>
       </c>
     </row>
@@ -6680,23 +6780,23 @@
         <v/>
       </c>
       <c r="F33" s="13">
-        <f>F25+F28*Assumptions!$C$36/100</f>
+        <f>F25+F28*Assumptions!$C$38/100</f>
         <v/>
       </c>
       <c r="G33" s="13">
-        <f>G25+G28*Assumptions!$C$36/100</f>
+        <f>G25+G28*Assumptions!$C$38/100</f>
         <v/>
       </c>
       <c r="H33" s="13">
-        <f>H25+H28*Assumptions!$C$36/100</f>
+        <f>H25+H28*Assumptions!$C$38/100</f>
         <v/>
       </c>
       <c r="I33" s="13">
-        <f>I25+I28*Assumptions!$C$36/100</f>
+        <f>I25+I28*Assumptions!$C$38/100</f>
         <v/>
       </c>
       <c r="J33" s="13">
-        <f>J25+J28*Assumptions!$C$36/100</f>
+        <f>J25+J28*Assumptions!$C$38/100</f>
         <v/>
       </c>
     </row>
@@ -6786,35 +6886,35 @@
         </is>
       </c>
       <c r="C37" s="13">
-        <f>Historicals!C43</f>
+        <f>Historicals!C45</f>
         <v/>
       </c>
       <c r="D37" s="13">
-        <f>Historicals!D43</f>
+        <f>Historicals!D45</f>
         <v/>
       </c>
       <c r="E37" s="13">
-        <f>Historicals!E43</f>
+        <f>Historicals!E45</f>
         <v/>
       </c>
       <c r="F37" s="13">
-        <f>F8*F12+F18*F22+F28*(1-Assumptions!$C$35/100)+Assumptions!F33</f>
+        <f>F8*F12+F18*F22+F28*(1-Assumptions!$C$37/100)+Assumptions!F35</f>
         <v/>
       </c>
       <c r="G37" s="13">
-        <f>G8*G12+G18*G22+G28*(1-Assumptions!$C$35/100)+Assumptions!G33</f>
+        <f>G8*G12+G18*G22+G28*(1-Assumptions!$C$37/100)+Assumptions!G35</f>
         <v/>
       </c>
       <c r="H37" s="13">
-        <f>H8*H12+H18*H22+H28*(1-Assumptions!$C$35/100)+Assumptions!H33</f>
+        <f>H8*H12+H18*H22+H28*(1-Assumptions!$C$37/100)+Assumptions!H35</f>
         <v/>
       </c>
       <c r="I37" s="13">
-        <f>I8*I12+I18*I22+I28*(1-Assumptions!$C$35/100)+Assumptions!I33</f>
+        <f>I8*I12+I18*I22+I28*(1-Assumptions!$C$37/100)+Assumptions!I35</f>
         <v/>
       </c>
       <c r="J37" s="13">
-        <f>J8*J12+J18*J22+J28*(1-Assumptions!$C$35/100)+Assumptions!J33</f>
+        <f>J8*J12+J18*J22+J28*(1-Assumptions!$C$37/100)+Assumptions!J35</f>
         <v/>
       </c>
     </row>
@@ -7432,35 +7532,35 @@
         </is>
       </c>
       <c r="C20" s="13">
-        <f>Historicals!C36+Historicals!C37</f>
+        <f>Historicals!C38+Historicals!C39</f>
         <v/>
       </c>
       <c r="D20" s="13">
-        <f>Historicals!D36+Historicals!D37</f>
+        <f>Historicals!D38+Historicals!D39</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>Historicals!E36+Historicals!E37</f>
+        <f>Historicals!E38+Historicals!E39</f>
         <v/>
       </c>
       <c r="F20" s="13">
-        <f>(F8+F9)*Assumptions!F30/100</f>
+        <f>(F8+F9)*Assumptions!F32/100</f>
         <v/>
       </c>
       <c r="G20" s="13">
-        <f>(G8+G9)*Assumptions!G30/100</f>
+        <f>(G8+G9)*Assumptions!G32/100</f>
         <v/>
       </c>
       <c r="H20" s="13">
-        <f>(H8+H9)*Assumptions!H30/100</f>
+        <f>(H8+H9)*Assumptions!H32/100</f>
         <v/>
       </c>
       <c r="I20" s="13">
-        <f>(I8+I9)*Assumptions!I30/100</f>
+        <f>(I8+I9)*Assumptions!I32/100</f>
         <v/>
       </c>
       <c r="J20" s="13">
-        <f>(J8+J9)*Assumptions!J30/100</f>
+        <f>(J8+J9)*Assumptions!J32/100</f>
         <v/>
       </c>
     </row>
@@ -7471,35 +7571,35 @@
         </is>
       </c>
       <c r="C21" s="13">
-        <f>Historicals!C38+Historicals!C39+Historicals!C40</f>
+        <f>Historicals!C40+Historicals!C41+Historicals!C42</f>
         <v/>
       </c>
       <c r="D21" s="13">
-        <f>Historicals!D38+Historicals!D39+Historicals!D40</f>
+        <f>Historicals!D40+Historicals!D41+Historicals!D42</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>Historicals!E38+Historicals!E39+Historicals!E40</f>
+        <f>Historicals!E40+Historicals!E41+Historicals!E42</f>
         <v/>
       </c>
       <c r="F21" s="13">
-        <f>(F8+F9)*Assumptions!F31/100+F10*(1-Assumptions!$C$37/100)</f>
+        <f>(F8+F9)*Assumptions!F33/100+F10*(1-Assumptions!$C$39/100)</f>
         <v/>
       </c>
       <c r="G21" s="13">
-        <f>(G8+G9)*Assumptions!G31/100+G10*(1-Assumptions!$C$37/100)</f>
+        <f>(G8+G9)*Assumptions!G33/100+G10*(1-Assumptions!$C$39/100)</f>
         <v/>
       </c>
       <c r="H21" s="13">
-        <f>(H8+H9)*Assumptions!H31/100+H10*(1-Assumptions!$C$37/100)</f>
+        <f>(H8+H9)*Assumptions!H33/100+H10*(1-Assumptions!$C$39/100)</f>
         <v/>
       </c>
       <c r="I21" s="13">
-        <f>(I8+I9)*Assumptions!I31/100+I10*(1-Assumptions!$C$37/100)</f>
+        <f>(I8+I9)*Assumptions!I33/100+I10*(1-Assumptions!$C$39/100)</f>
         <v/>
       </c>
       <c r="J21" s="13">
-        <f>(J8+J9)*Assumptions!J31/100+J10*(1-Assumptions!$C$37/100)</f>
+        <f>(J8+J9)*Assumptions!J33/100+J10*(1-Assumptions!$C$39/100)</f>
         <v/>
       </c>
     </row>
@@ -7510,35 +7610,35 @@
         </is>
       </c>
       <c r="C22" s="13">
-        <f>-Historicals!C32</f>
+        <f>-Historicals!C34</f>
         <v/>
       </c>
       <c r="D22" s="13">
-        <f>-Historicals!D32</f>
+        <f>-Historicals!D34</f>
         <v/>
       </c>
       <c r="E22" s="13">
-        <f>-Historicals!E32</f>
+        <f>-Historicals!E34</f>
         <v/>
       </c>
       <c r="F22" s="13">
-        <f>-Assumptions!F32</f>
+        <f>-Assumptions!F34</f>
         <v/>
       </c>
       <c r="G22" s="13">
-        <f>-Assumptions!G32</f>
+        <f>-Assumptions!G34</f>
         <v/>
       </c>
       <c r="H22" s="13">
-        <f>-Assumptions!H32</f>
+        <f>-Assumptions!H34</f>
         <v/>
       </c>
       <c r="I22" s="13">
-        <f>-Assumptions!I32</f>
+        <f>-Assumptions!I34</f>
         <v/>
       </c>
       <c r="J22" s="13">
-        <f>-Assumptions!J32</f>
+        <f>-Assumptions!J34</f>
         <v/>
       </c>
     </row>
@@ -7706,35 +7806,35 @@
         </is>
       </c>
       <c r="C28" s="13">
-        <f>Historicals!C44-Historicals!C33</f>
+        <f>Historicals!C46-Historicals!C35</f>
         <v/>
       </c>
       <c r="D28" s="13">
-        <f>Historicals!D44-Historicals!D33</f>
+        <f>Historicals!D46-Historicals!D35</f>
         <v/>
       </c>
       <c r="E28" s="13">
-        <f>Historicals!E44-Historicals!E33</f>
+        <f>Historicals!E46-Historicals!E35</f>
         <v/>
       </c>
       <c r="F28" s="13">
-        <f>Assumptions!F34</f>
+        <f>Assumptions!F36</f>
         <v/>
       </c>
       <c r="G28" s="13">
-        <f>Assumptions!G34</f>
+        <f>Assumptions!G36</f>
         <v/>
       </c>
       <c r="H28" s="13">
-        <f>Assumptions!H34</f>
+        <f>Assumptions!H36</f>
         <v/>
       </c>
       <c r="I28" s="13">
-        <f>Assumptions!I34</f>
+        <f>Assumptions!I36</f>
         <v/>
       </c>
       <c r="J28" s="13">
-        <f>Assumptions!J34</f>
+        <f>Assumptions!J36</f>
         <v/>
       </c>
     </row>
@@ -7784,35 +7884,35 @@
         </is>
       </c>
       <c r="C30" s="13">
-        <f>Historicals!C45</f>
+        <f>Historicals!C47</f>
         <v/>
       </c>
       <c r="D30" s="13">
-        <f>Historicals!D45</f>
+        <f>Historicals!D47</f>
         <v/>
       </c>
       <c r="E30" s="13">
-        <f>Historicals!E45</f>
+        <f>Historicals!E47</f>
         <v/>
       </c>
       <c r="F30" s="13">
-        <f>F29*Assumptions!$C$38/100</f>
+        <f>F29*Assumptions!$C$40/100</f>
         <v/>
       </c>
       <c r="G30" s="13">
-        <f>G29*Assumptions!$C$38/100</f>
+        <f>G29*Assumptions!$C$40/100</f>
         <v/>
       </c>
       <c r="H30" s="13">
-        <f>H29*Assumptions!$C$38/100</f>
+        <f>H29*Assumptions!$C$40/100</f>
         <v/>
       </c>
       <c r="I30" s="13">
-        <f>I29*Assumptions!$C$38/100</f>
+        <f>I29*Assumptions!$C$40/100</f>
         <v/>
       </c>
       <c r="J30" s="13">
-        <f>J29*Assumptions!$C$38/100</f>
+        <f>J29*Assumptions!$C$40/100</f>
         <v/>
       </c>
     </row>
@@ -7956,35 +8056,35 @@
         </is>
       </c>
       <c r="C36" s="13">
-        <f>Historicals!C48</f>
+        <f>Historicals!C50</f>
         <v/>
       </c>
       <c r="D36" s="13">
-        <f>Historicals!D48</f>
+        <f>Historicals!D50</f>
         <v/>
       </c>
       <c r="E36" s="13">
-        <f>Historicals!E48</f>
+        <f>Historicals!E50</f>
         <v/>
       </c>
       <c r="F36" s="13">
-        <f>E36-Assumptions!F47/Assumptions!F48+Assumptions!F49</f>
+        <f>E36-Assumptions!F49/Assumptions!F50+Assumptions!F51</f>
         <v/>
       </c>
       <c r="G36" s="13">
-        <f>F36-Assumptions!G47/Assumptions!G48+Assumptions!G49</f>
+        <f>F36-Assumptions!G49/Assumptions!G50+Assumptions!G51</f>
         <v/>
       </c>
       <c r="H36" s="13">
-        <f>G36-Assumptions!H47/Assumptions!H48+Assumptions!H49</f>
+        <f>G36-Assumptions!H49/Assumptions!H50+Assumptions!H51</f>
         <v/>
       </c>
       <c r="I36" s="13">
-        <f>H36-Assumptions!I47/Assumptions!I48+Assumptions!I49</f>
+        <f>H36-Assumptions!I49/Assumptions!I50+Assumptions!I51</f>
         <v/>
       </c>
       <c r="J36" s="13">
-        <f>I36-Assumptions!J47/Assumptions!J48+Assumptions!J49</f>
+        <f>I36-Assumptions!J49/Assumptions!J50+Assumptions!J51</f>
         <v/>
       </c>
     </row>
@@ -8085,35 +8185,35 @@
         </is>
       </c>
       <c r="C41" s="13">
-        <f>Historicals!C29</f>
+        <f>Historicals!C31</f>
         <v/>
       </c>
       <c r="D41" s="13">
-        <f>Historicals!D29</f>
+        <f>Historicals!D31</f>
         <v/>
       </c>
       <c r="E41" s="13">
-        <f>Historicals!E29</f>
+        <f>Historicals!E31</f>
         <v/>
       </c>
       <c r="F41" s="13">
-        <f>F8-('Segment Build'!F8*'Segment Build'!F12+'Segment Build'!F28*(1-Assumptions!$C$36/100)*(1-Assumptions!$C$35/100)+Assumptions!F33*0.25)-(F20+(F8+F9)*Assumptions!F31/100)*F8/(F8+F9)</f>
+        <f>F8-('Segment Build'!F8*'Segment Build'!F12+'Segment Build'!F28*(1-Assumptions!$C$38/100)*(1-Assumptions!$C$37/100)+Assumptions!F35*0.25)-(F20+(F8+F9)*Assumptions!F33/100)*F8/(F8+F9)</f>
         <v/>
       </c>
       <c r="G41" s="13">
-        <f>G8-('Segment Build'!G8*'Segment Build'!G12+'Segment Build'!G28*(1-Assumptions!$C$36/100)*(1-Assumptions!$C$35/100)+Assumptions!G33*0.25)-(G20+(G8+G9)*Assumptions!G31/100)*G8/(G8+G9)</f>
+        <f>G8-('Segment Build'!G8*'Segment Build'!G12+'Segment Build'!G28*(1-Assumptions!$C$38/100)*(1-Assumptions!$C$37/100)+Assumptions!G35*0.25)-(G20+(G8+G9)*Assumptions!G33/100)*G8/(G8+G9)</f>
         <v/>
       </c>
       <c r="H41" s="13">
-        <f>H8-('Segment Build'!H8*'Segment Build'!H12+'Segment Build'!H28*(1-Assumptions!$C$36/100)*(1-Assumptions!$C$35/100)+Assumptions!H33*0.25)-(H20+(H8+H9)*Assumptions!H31/100)*H8/(H8+H9)</f>
+        <f>H8-('Segment Build'!H8*'Segment Build'!H12+'Segment Build'!H28*(1-Assumptions!$C$38/100)*(1-Assumptions!$C$37/100)+Assumptions!H35*0.25)-(H20+(H8+H9)*Assumptions!H33/100)*H8/(H8+H9)</f>
         <v/>
       </c>
       <c r="I41" s="13">
-        <f>I8-('Segment Build'!I8*'Segment Build'!I12+'Segment Build'!I28*(1-Assumptions!$C$36/100)*(1-Assumptions!$C$35/100)+Assumptions!I33*0.25)-(I20+(I8+I9)*Assumptions!I31/100)*I8/(I8+I9)</f>
+        <f>I8-('Segment Build'!I8*'Segment Build'!I12+'Segment Build'!I28*(1-Assumptions!$C$38/100)*(1-Assumptions!$C$37/100)+Assumptions!I35*0.25)-(I20+(I8+I9)*Assumptions!I33/100)*I8/(I8+I9)</f>
         <v/>
       </c>
       <c r="J41" s="13">
-        <f>J8-('Segment Build'!J8*'Segment Build'!J12+'Segment Build'!J28*(1-Assumptions!$C$36/100)*(1-Assumptions!$C$35/100)+Assumptions!J33*0.25)-(J20+(J8+J9)*Assumptions!J31/100)*J8/(J8+J9)</f>
+        <f>J8-('Segment Build'!J8*'Segment Build'!J12+'Segment Build'!J28*(1-Assumptions!$C$38/100)*(1-Assumptions!$C$37/100)+Assumptions!J35*0.25)-(J20+(J8+J9)*Assumptions!J33/100)*J8/(J8+J9)</f>
         <v/>
       </c>
     </row>
@@ -8124,35 +8224,35 @@
         </is>
       </c>
       <c r="C42" s="13">
-        <f>Historicals!C30</f>
+        <f>Historicals!C32</f>
         <v/>
       </c>
       <c r="D42" s="13">
-        <f>Historicals!D30</f>
+        <f>Historicals!D32</f>
         <v/>
       </c>
       <c r="E42" s="13">
-        <f>Historicals!E30</f>
+        <f>Historicals!E32</f>
         <v/>
       </c>
       <c r="F42" s="13">
-        <f>F9-('Segment Build'!F18*'Segment Build'!F22+'Segment Build'!F28*Assumptions!$C$36/100*(1-Assumptions!$C$35/100)+Assumptions!F33*0.75)-(F20+(F8+F9)*Assumptions!F31/100)*F9/(F8+F9)</f>
+        <f>F9-('Segment Build'!F18*'Segment Build'!F22+'Segment Build'!F28*Assumptions!$C$38/100*(1-Assumptions!$C$37/100)+Assumptions!F35*0.75)-(F20+(F8+F9)*Assumptions!F33/100)*F9/(F8+F9)</f>
         <v/>
       </c>
       <c r="G42" s="13">
-        <f>G9-('Segment Build'!G18*'Segment Build'!G22+'Segment Build'!G28*Assumptions!$C$36/100*(1-Assumptions!$C$35/100)+Assumptions!G33*0.75)-(G20+(G8+G9)*Assumptions!G31/100)*G9/(G8+G9)</f>
+        <f>G9-('Segment Build'!G18*'Segment Build'!G22+'Segment Build'!G28*Assumptions!$C$38/100*(1-Assumptions!$C$37/100)+Assumptions!G35*0.75)-(G20+(G8+G9)*Assumptions!G33/100)*G9/(G8+G9)</f>
         <v/>
       </c>
       <c r="H42" s="13">
-        <f>H9-('Segment Build'!H18*'Segment Build'!H22+'Segment Build'!H28*Assumptions!$C$36/100*(1-Assumptions!$C$35/100)+Assumptions!H33*0.75)-(H20+(H8+H9)*Assumptions!H31/100)*H9/(H8+H9)</f>
+        <f>H9-('Segment Build'!H18*'Segment Build'!H22+'Segment Build'!H28*Assumptions!$C$38/100*(1-Assumptions!$C$37/100)+Assumptions!H35*0.75)-(H20+(H8+H9)*Assumptions!H33/100)*H9/(H8+H9)</f>
         <v/>
       </c>
       <c r="I42" s="13">
-        <f>I9-('Segment Build'!I18*'Segment Build'!I22+'Segment Build'!I28*Assumptions!$C$36/100*(1-Assumptions!$C$35/100)+Assumptions!I33*0.75)-(I20+(I8+I9)*Assumptions!I31/100)*I9/(I8+I9)</f>
+        <f>I9-('Segment Build'!I18*'Segment Build'!I22+'Segment Build'!I28*Assumptions!$C$38/100*(1-Assumptions!$C$37/100)+Assumptions!I35*0.75)-(I20+(I8+I9)*Assumptions!I33/100)*I9/(I8+I9)</f>
         <v/>
       </c>
       <c r="J42" s="13">
-        <f>J9-('Segment Build'!J18*'Segment Build'!J22+'Segment Build'!J28*Assumptions!$C$36/100*(1-Assumptions!$C$35/100)+Assumptions!J33*0.75)-(J20+(J8+J9)*Assumptions!J31/100)*J9/(J8+J9)</f>
+        <f>J9-('Segment Build'!J18*'Segment Build'!J22+'Segment Build'!J28*Assumptions!$C$38/100*(1-Assumptions!$C$37/100)+Assumptions!J35*0.75)-(J20+(J8+J9)*Assumptions!J33/100)*J9/(J8+J9)</f>
         <v/>
       </c>
     </row>
@@ -8163,35 +8263,35 @@
         </is>
       </c>
       <c r="C43" s="13">
-        <f>Historicals!C31</f>
+        <f>Historicals!C33</f>
         <v/>
       </c>
       <c r="D43" s="13">
-        <f>Historicals!D31</f>
+        <f>Historicals!D33</f>
         <v/>
       </c>
       <c r="E43" s="13">
-        <f>Historicals!E31</f>
+        <f>Historicals!E33</f>
         <v/>
       </c>
       <c r="F43" s="13">
-        <f>F10*Assumptions!$C$37/100</f>
+        <f>F10*Assumptions!$C$39/100</f>
         <v/>
       </c>
       <c r="G43" s="13">
-        <f>G10*Assumptions!$C$37/100</f>
+        <f>G10*Assumptions!$C$39/100</f>
         <v/>
       </c>
       <c r="H43" s="13">
-        <f>H10*Assumptions!$C$37/100</f>
+        <f>H10*Assumptions!$C$39/100</f>
         <v/>
       </c>
       <c r="I43" s="13">
-        <f>I10*Assumptions!$C$37/100</f>
+        <f>I10*Assumptions!$C$39/100</f>
         <v/>
       </c>
       <c r="J43" s="13">
-        <f>J10*Assumptions!$C$37/100</f>
+        <f>J10*Assumptions!$C$39/100</f>
         <v/>
       </c>
     </row>
@@ -8391,15 +8491,15 @@
         </is>
       </c>
       <c r="C8" s="51">
-        <f>Historicals!C52</f>
+        <f>Historicals!C54</f>
         <v/>
       </c>
       <c r="D8" s="51">
-        <f>Historicals!D52</f>
+        <f>Historicals!D54</f>
         <v/>
       </c>
       <c r="E8" s="51">
-        <f>Historicals!E52</f>
+        <f>Historicals!E54</f>
         <v/>
       </c>
       <c r="F8" s="51">
@@ -8430,35 +8530,35 @@
         </is>
       </c>
       <c r="C9" s="13">
-        <f>Historicals!C53</f>
+        <f>Historicals!C55</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>Historicals!D53</f>
+        <f>Historicals!D55</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>Historicals!E53</f>
+        <f>Historicals!E55</f>
         <v/>
       </c>
       <c r="F9" s="13">
-        <f>'Segment Build'!F34/Assumptions!F41</f>
+        <f>MAX('Segment Build'!F34/Assumptions!F43,E9)</f>
         <v/>
       </c>
       <c r="G9" s="13">
-        <f>'Segment Build'!G34/Assumptions!G41</f>
+        <f>MAX('Segment Build'!G34/Assumptions!G43,F9)</f>
         <v/>
       </c>
       <c r="H9" s="13">
-        <f>'Segment Build'!H34/Assumptions!H41</f>
+        <f>MAX('Segment Build'!H34/Assumptions!H43,G9)</f>
         <v/>
       </c>
       <c r="I9" s="13">
-        <f>'Segment Build'!I34/Assumptions!I41</f>
+        <f>MAX('Segment Build'!I34/Assumptions!I43,H9)</f>
         <v/>
       </c>
       <c r="J9" s="13">
-        <f>'Segment Build'!J34/Assumptions!J41</f>
+        <f>MAX('Segment Build'!J34/Assumptions!J43,I9)</f>
         <v/>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -8474,35 +8574,35 @@
         </is>
       </c>
       <c r="C10" s="13">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>Assumptions!$C$52</f>
+        <f>Assumptions!$C$54</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>E10+Assumptions!F44-Assumptions!F45</f>
+        <f>E10+Assumptions!F46-Assumptions!F47</f>
         <v/>
       </c>
       <c r="G10" s="13">
-        <f>F10+Assumptions!G44-Assumptions!G45</f>
+        <f>F10+Assumptions!G46-Assumptions!G47</f>
         <v/>
       </c>
       <c r="H10" s="13">
-        <f>G10+Assumptions!H44-Assumptions!H45</f>
+        <f>G10+Assumptions!H46-Assumptions!H47</f>
         <v/>
       </c>
       <c r="I10" s="13">
-        <f>H10+Assumptions!I44-Assumptions!I45</f>
+        <f>H10+Assumptions!I46-Assumptions!I47</f>
         <v/>
       </c>
       <c r="J10" s="13">
-        <f>I10+Assumptions!J44-Assumptions!J45</f>
+        <f>I10+Assumptions!J46-Assumptions!J47</f>
         <v/>
       </c>
     </row>
@@ -8513,35 +8613,35 @@
         </is>
       </c>
       <c r="C11" s="13">
-        <f>Historicals!C54-C8-C9-C10</f>
+        <f>Historicals!C56-C8-C9-C10</f>
         <v/>
       </c>
       <c r="D11" s="13">
-        <f>Historicals!D54-D8-D9-D10</f>
+        <f>Historicals!D56-D8-D9-D10</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>Historicals!E54-E8-E9-E10</f>
+        <f>Historicals!E56-E8-E9-E10</f>
         <v/>
       </c>
       <c r="F11" s="13">
-        <f>IS!F11*Assumptions!F42/100</f>
+        <f>IS!F11*Assumptions!F44/100</f>
         <v/>
       </c>
       <c r="G11" s="13">
-        <f>IS!G11*Assumptions!G42/100</f>
+        <f>IS!G11*Assumptions!G44/100</f>
         <v/>
       </c>
       <c r="H11" s="13">
-        <f>IS!H11*Assumptions!H42/100</f>
+        <f>IS!H11*Assumptions!H44/100</f>
         <v/>
       </c>
       <c r="I11" s="13">
-        <f>IS!I11*Assumptions!I42/100</f>
+        <f>IS!I11*Assumptions!I44/100</f>
         <v/>
       </c>
       <c r="J11" s="13">
-        <f>IS!J11*Assumptions!J42/100</f>
+        <f>IS!J11*Assumptions!J44/100</f>
         <v/>
       </c>
     </row>
@@ -8607,35 +8707,35 @@
         </is>
       </c>
       <c r="C15" s="51">
-        <f>Historicals!C55</f>
+        <f>Historicals!C57</f>
         <v/>
       </c>
       <c r="D15" s="51">
-        <f>Historicals!D55</f>
+        <f>Historicals!D57</f>
         <v/>
       </c>
       <c r="E15" s="51">
-        <f>Historicals!E55</f>
+        <f>Historicals!E57</f>
         <v/>
       </c>
       <c r="F15" s="51">
-        <f>Assumptions!F50</f>
+        <f>Assumptions!F52</f>
         <v/>
       </c>
       <c r="G15" s="51">
-        <f>Assumptions!G50</f>
+        <f>Assumptions!G52</f>
         <v/>
       </c>
       <c r="H15" s="51">
-        <f>Assumptions!H50</f>
+        <f>Assumptions!H52</f>
         <v/>
       </c>
       <c r="I15" s="51">
-        <f>Assumptions!I50</f>
+        <f>Assumptions!I52</f>
         <v/>
       </c>
       <c r="J15" s="51">
-        <f>Assumptions!J50</f>
+        <f>Assumptions!J52</f>
         <v/>
       </c>
     </row>
@@ -8646,35 +8746,35 @@
         </is>
       </c>
       <c r="C16" s="51">
-        <f>Historicals!C56</f>
+        <f>Historicals!C58</f>
         <v/>
       </c>
       <c r="D16" s="51">
-        <f>Historicals!D56</f>
+        <f>Historicals!D58</f>
         <v/>
       </c>
       <c r="E16" s="51">
-        <f>Historicals!E56</f>
+        <f>Historicals!E58</f>
         <v/>
       </c>
       <c r="F16" s="51">
-        <f>Assumptions!F51</f>
+        <f>Assumptions!F53</f>
         <v/>
       </c>
       <c r="G16" s="51">
-        <f>Assumptions!G51</f>
+        <f>Assumptions!G53</f>
         <v/>
       </c>
       <c r="H16" s="51">
-        <f>Assumptions!H51</f>
+        <f>Assumptions!H53</f>
         <v/>
       </c>
       <c r="I16" s="51">
-        <f>Assumptions!I51</f>
+        <f>Assumptions!I53</f>
         <v/>
       </c>
       <c r="J16" s="51">
-        <f>Assumptions!J51</f>
+        <f>Assumptions!J53</f>
         <v/>
       </c>
     </row>
@@ -8685,35 +8785,35 @@
         </is>
       </c>
       <c r="C17" s="13">
-        <f>Historicals!C54-Historicals!C57-C15-C16</f>
+        <f>Historicals!C56-Historicals!C59-C15-C16</f>
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>Historicals!D54-Historicals!D57-D15-D16</f>
+        <f>Historicals!D56-Historicals!D59-D15-D16</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>Historicals!E54-Historicals!E57-E15-E16</f>
+        <f>Historicals!E56-Historicals!E59-E15-E16</f>
         <v/>
       </c>
       <c r="F17" s="13">
-        <f>IS!F11*Assumptions!F43/100</f>
+        <f>IS!F11*Assumptions!F45/100</f>
         <v/>
       </c>
       <c r="G17" s="13">
-        <f>IS!G11*Assumptions!G43/100</f>
+        <f>IS!G11*Assumptions!G45/100</f>
         <v/>
       </c>
       <c r="H17" s="13">
-        <f>IS!H11*Assumptions!H43/100</f>
+        <f>IS!H11*Assumptions!H45/100</f>
         <v/>
       </c>
       <c r="I17" s="13">
-        <f>IS!I11*Assumptions!I43/100</f>
+        <f>IS!I11*Assumptions!I45/100</f>
         <v/>
       </c>
       <c r="J17" s="13">
-        <f>IS!J11*Assumptions!J43/100</f>
+        <f>IS!J11*Assumptions!J45/100</f>
         <v/>
       </c>
     </row>
@@ -8763,35 +8863,35 @@
         </is>
       </c>
       <c r="C19" s="58">
-        <f>Historicals!C57</f>
+        <f>Historicals!C59</f>
         <v/>
       </c>
       <c r="D19" s="58">
-        <f>Historicals!D57</f>
+        <f>Historicals!D59</f>
         <v/>
       </c>
       <c r="E19" s="58">
-        <f>Historicals!E57</f>
+        <f>Historicals!E59</f>
         <v/>
       </c>
       <c r="F19" s="58">
-        <f>E19+IS!F32+Assumptions!F46-Assumptions!F47</f>
+        <f>E19+IS!F32+Assumptions!F48-Assumptions!F49</f>
         <v/>
       </c>
       <c r="G19" s="58">
-        <f>F19+IS!G32+Assumptions!G46-Assumptions!G47</f>
+        <f>F19+IS!G32+Assumptions!G48-Assumptions!G49</f>
         <v/>
       </c>
       <c r="H19" s="58">
-        <f>G19+IS!H32+Assumptions!H46-Assumptions!H47</f>
+        <f>G19+IS!H32+Assumptions!H48-Assumptions!H49</f>
         <v/>
       </c>
       <c r="I19" s="58">
-        <f>H19+IS!I32+Assumptions!I46-Assumptions!I47</f>
+        <f>H19+IS!I32+Assumptions!I48-Assumptions!I49</f>
         <v/>
       </c>
       <c r="J19" s="58">
-        <f>I19+IS!J32+Assumptions!J46-Assumptions!J47</f>
+        <f>I19+IS!J32+Assumptions!J48-Assumptions!J49</f>
         <v/>
       </c>
     </row>
@@ -8901,15 +9001,15 @@
         </is>
       </c>
       <c r="C24" s="13">
-        <f>Historicals!C49</f>
+        <f>Historicals!C51</f>
         <v/>
       </c>
       <c r="D24" s="13">
-        <f>Historicals!D49</f>
+        <f>Historicals!D51</f>
         <v/>
       </c>
       <c r="E24" s="13">
-        <f>Historicals!E49</f>
+        <f>Historicals!E51</f>
         <v/>
       </c>
       <c r="F24" s="13">
@@ -9334,35 +9434,35 @@
         </is>
       </c>
       <c r="C9" s="13">
-        <f>Historicals!C59</f>
+        <f>Historicals!C61</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>Historicals!D59</f>
+        <f>Historicals!D61</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>Historicals!E59</f>
+        <f>Historicals!E61</f>
         <v/>
       </c>
       <c r="F9" s="13">
-        <f>Assumptions!F45</f>
+        <f>Assumptions!F47</f>
         <v/>
       </c>
       <c r="G9" s="13">
-        <f>Assumptions!G45</f>
+        <f>Assumptions!G47</f>
         <v/>
       </c>
       <c r="H9" s="13">
-        <f>Assumptions!H45</f>
+        <f>Assumptions!H47</f>
         <v/>
       </c>
       <c r="I9" s="13">
-        <f>Assumptions!I45</f>
+        <f>Assumptions!I47</f>
         <v/>
       </c>
       <c r="J9" s="13">
-        <f>Assumptions!J45</f>
+        <f>Assumptions!J47</f>
         <v/>
       </c>
     </row>
@@ -9373,35 +9473,35 @@
         </is>
       </c>
       <c r="C10" s="13">
-        <f>Historicals!C60</f>
+        <f>Historicals!C62</f>
         <v/>
       </c>
       <c r="D10" s="13">
-        <f>Historicals!D60</f>
+        <f>Historicals!D62</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>Historicals!E60</f>
+        <f>Historicals!E62</f>
         <v/>
       </c>
       <c r="F10" s="13">
-        <f>Assumptions!F46</f>
+        <f>Assumptions!F48</f>
         <v/>
       </c>
       <c r="G10" s="13">
-        <f>Assumptions!G46</f>
+        <f>Assumptions!G48</f>
         <v/>
       </c>
       <c r="H10" s="13">
-        <f>Assumptions!H46</f>
+        <f>Assumptions!H48</f>
         <v/>
       </c>
       <c r="I10" s="13">
-        <f>Assumptions!I46</f>
+        <f>Assumptions!I48</f>
         <v/>
       </c>
       <c r="J10" s="13">
-        <f>Assumptions!J46</f>
+        <f>Assumptions!J48</f>
         <v/>
       </c>
     </row>
@@ -9498,15 +9598,15 @@
         </is>
       </c>
       <c r="C14" s="45">
-        <f>Historicals!C58</f>
+        <f>Historicals!C60</f>
         <v/>
       </c>
       <c r="D14" s="45">
-        <f>Historicals!D58</f>
+        <f>Historicals!D60</f>
         <v/>
       </c>
       <c r="E14" s="45">
-        <f>Historicals!E58</f>
+        <f>Historicals!E60</f>
         <v/>
       </c>
       <c r="F14" s="45">
@@ -9553,35 +9653,35 @@
         </is>
       </c>
       <c r="C17" s="13">
-        <f>-Historicals!C61</f>
+        <f>-Historicals!C63</f>
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>-Historicals!D61</f>
+        <f>-Historicals!D63</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>-Historicals!E61</f>
+        <f>-Historicals!E63</f>
         <v/>
       </c>
       <c r="F17" s="13">
-        <f>-Assumptions!F44</f>
+        <f>-Assumptions!F46</f>
         <v/>
       </c>
       <c r="G17" s="13">
-        <f>-Assumptions!G44</f>
+        <f>-Assumptions!G46</f>
         <v/>
       </c>
       <c r="H17" s="13">
-        <f>-Assumptions!H44</f>
+        <f>-Assumptions!H46</f>
         <v/>
       </c>
       <c r="I17" s="13">
-        <f>-Assumptions!I44</f>
+        <f>-Assumptions!I46</f>
         <v/>
       </c>
       <c r="J17" s="13">
-        <f>-Assumptions!J44</f>
+        <f>-Assumptions!J46</f>
         <v/>
       </c>
     </row>
@@ -9674,35 +9774,35 @@
         </is>
       </c>
       <c r="C22" s="13">
-        <f>-Historicals!C62</f>
+        <f>-Historicals!C64</f>
         <v/>
       </c>
       <c r="D22" s="13">
-        <f>-Historicals!D62</f>
+        <f>-Historicals!D64</f>
         <v/>
       </c>
       <c r="E22" s="13">
-        <f>-Historicals!E62</f>
+        <f>-Historicals!E64</f>
         <v/>
       </c>
       <c r="F22" s="13">
-        <f>-Assumptions!F47</f>
+        <f>-Assumptions!F49</f>
         <v/>
       </c>
       <c r="G22" s="13">
-        <f>-Assumptions!G47</f>
+        <f>-Assumptions!G49</f>
         <v/>
       </c>
       <c r="H22" s="13">
-        <f>-Assumptions!H47</f>
+        <f>-Assumptions!H49</f>
         <v/>
       </c>
       <c r="I22" s="13">
-        <f>-Assumptions!I47</f>
+        <f>-Assumptions!I49</f>
         <v/>
       </c>
       <c r="J22" s="13">
-        <f>-Assumptions!J47</f>
+        <f>-Assumptions!J49</f>
         <v/>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -9779,7 +9879,7 @@
         </is>
       </c>
       <c r="F26" s="13">
-        <f>Historicals!E52</f>
+        <f>Historicals!E54</f>
         <v/>
       </c>
       <c r="G26" s="13">
@@ -9806,15 +9906,15 @@
         </is>
       </c>
       <c r="C27" s="45">
-        <f>Historicals!C52</f>
+        <f>Historicals!C54</f>
         <v/>
       </c>
       <c r="D27" s="45">
-        <f>Historicals!D52</f>
+        <f>Historicals!D54</f>
         <v/>
       </c>
       <c r="E27" s="45">
-        <f>Historicals!E52</f>
+        <f>Historicals!E54</f>
         <v/>
       </c>
       <c r="F27" s="45">
@@ -9949,7 +10049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L53"/>
+  <dimension ref="B2:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.2" customWidth="1" min="1" max="1"/>
@@ -10002,7 +10102,7 @@
         </is>
       </c>
       <c r="C6" s="52">
-        <f>Assumptions!$C$55</f>
+        <f>Assumptions!$C$57</f>
         <v/>
       </c>
     </row>
@@ -10013,7 +10113,7 @@
         </is>
       </c>
       <c r="C7" s="52">
-        <f>Assumptions!$C$56</f>
+        <f>Assumptions!$C$58</f>
         <v/>
       </c>
     </row>
@@ -10024,7 +10124,7 @@
         </is>
       </c>
       <c r="C8" s="50">
-        <f>Assumptions!$C$57</f>
+        <f>Assumptions!$C$59</f>
         <v/>
       </c>
     </row>
@@ -10046,7 +10146,7 @@
         </is>
       </c>
       <c r="C10" s="52">
-        <f>Assumptions!$C$58</f>
+        <f>Assumptions!$C$60</f>
         <v/>
       </c>
     </row>
@@ -10057,7 +10157,7 @@
         </is>
       </c>
       <c r="C11" s="52">
-        <f>C10*(1-Assumptions!$C$38/100)</f>
+        <f>C10*(1-Assumptions!$C$40/100)</f>
         <v/>
       </c>
     </row>
@@ -10068,7 +10168,7 @@
         </is>
       </c>
       <c r="C12" s="13">
-        <f>Assumptions!$C$60*Assumptions!$C$61</f>
+        <f>Assumptions!$C$62*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -10133,7 +10233,7 @@
         </is>
       </c>
       <c r="C17" s="52">
-        <f>Assumptions!$C$59</f>
+        <f>Assumptions!$C$61</f>
         <v/>
       </c>
     </row>
@@ -10222,23 +10322,23 @@
         </is>
       </c>
       <c r="F22" s="13">
-        <f>-F21*Assumptions!$C$38/100</f>
+        <f>-F21*Assumptions!$C$40/100</f>
         <v/>
       </c>
       <c r="G22" s="13">
-        <f>-G21*Assumptions!$C$38/100</f>
+        <f>-G21*Assumptions!$C$40/100</f>
         <v/>
       </c>
       <c r="H22" s="13">
-        <f>-H21*Assumptions!$C$38/100</f>
+        <f>-H21*Assumptions!$C$40/100</f>
         <v/>
       </c>
       <c r="I22" s="13">
-        <f>-I21*Assumptions!$C$38/100</f>
+        <f>-I21*Assumptions!$C$40/100</f>
         <v/>
       </c>
       <c r="J22" s="13">
-        <f>-J21*Assumptions!$C$38/100</f>
+        <f>-J21*Assumptions!$C$40/100</f>
         <v/>
       </c>
     </row>
@@ -10276,23 +10376,23 @@
         </is>
       </c>
       <c r="F24" s="13">
-        <f>Assumptions!F45</f>
+        <f>Assumptions!F47</f>
         <v/>
       </c>
       <c r="G24" s="13">
-        <f>Assumptions!G45</f>
+        <f>Assumptions!G47</f>
         <v/>
       </c>
       <c r="H24" s="13">
-        <f>Assumptions!H45</f>
+        <f>Assumptions!H47</f>
         <v/>
       </c>
       <c r="I24" s="13">
-        <f>Assumptions!I45</f>
+        <f>Assumptions!I47</f>
         <v/>
       </c>
       <c r="J24" s="13">
-        <f>Assumptions!J45</f>
+        <f>Assumptions!J47</f>
         <v/>
       </c>
     </row>
@@ -10303,23 +10403,23 @@
         </is>
       </c>
       <c r="F25" s="13">
-        <f>-Assumptions!F44</f>
+        <f>-Assumptions!F46</f>
         <v/>
       </c>
       <c r="G25" s="13">
-        <f>-Assumptions!G44</f>
+        <f>-Assumptions!G46</f>
         <v/>
       </c>
       <c r="H25" s="13">
-        <f>-Assumptions!H44</f>
+        <f>-Assumptions!H46</f>
         <v/>
       </c>
       <c r="I25" s="13">
-        <f>-Assumptions!I44</f>
+        <f>-Assumptions!I46</f>
         <v/>
       </c>
       <c r="J25" s="13">
-        <f>-Assumptions!J44</f>
+        <f>-Assumptions!J46</f>
         <v/>
       </c>
     </row>
@@ -10330,23 +10430,23 @@
         </is>
       </c>
       <c r="F26" s="13">
-        <f>-Assumptions!F46</f>
+        <f>-Assumptions!F48</f>
         <v/>
       </c>
       <c r="G26" s="13">
-        <f>-Assumptions!G46</f>
+        <f>-Assumptions!G48</f>
         <v/>
       </c>
       <c r="H26" s="13">
-        <f>-Assumptions!H46</f>
+        <f>-Assumptions!H48</f>
         <v/>
       </c>
       <c r="I26" s="13">
-        <f>-Assumptions!I46</f>
+        <f>-Assumptions!I48</f>
         <v/>
       </c>
       <c r="J26" s="13">
-        <f>-Assumptions!J46</f>
+        <f>-Assumptions!J48</f>
         <v/>
       </c>
       <c r="L26" s="9" t="inlineStr">
@@ -10573,282 +10673,330 @@
     <row r="37">
       <c r="B37" s="10" t="inlineStr">
         <is>
-          <t>Terminal value at 31-Dec-2030</t>
-        </is>
-      </c>
-      <c r="C37" s="13">
-        <f>J29*(1+C17/100)/(C16/100-C17/100)</f>
+          <t>2030E revenue growth</t>
+        </is>
+      </c>
+      <c r="C37" s="16">
+        <f>IS!J11/IS!I11-1</f>
         <v/>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Gordon growth on 2030E free cash flow.</t>
+          <t>The growth the 2030 working capital build actually supports.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Present value of terminal value</t>
+          <t>Normalised terminal working capital investment</t>
         </is>
       </c>
       <c r="C38" s="13">
-        <f>C37/(1+C16/100)^4.25</f>
-        <v/>
+        <f>-J28*(C17/100)/C37</f>
+        <v/>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>The 2030 build scaled down to the perpetual growth rate.</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Terminal value as % of enterprise value</t>
-        </is>
-      </c>
-      <c r="C39" s="16">
-        <f>C38/(C36+C38)</f>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>NORMALISED TERMINAL FREE CASH FLOW</t>
+        </is>
+      </c>
+      <c r="C39" s="64">
+        <f>J29+(-J28)-C38</f>
         <v/>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>High, as it always is for a cyclical with heavy near-term working capital investment. Treat the DCF as a discipline, not an oracle.</t>
+          <t>This, not 2030E FCF, is what the terminal value is built on.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>ENTERPRISE VALUE</t>
-        </is>
-      </c>
-      <c r="C40" s="64">
-        <f>C36+C38</f>
-        <v/>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Terminal value at 31-Dec-2030</t>
+        </is>
+      </c>
+      <c r="C40" s="13">
+        <f>C39*(1+C17/100)/(C16/100-C17/100)</f>
+        <v/>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Gordon growth on the NORMALISED terminal cash flow.</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="10" t="inlineStr">
         <is>
+          <t>Present value of terminal value</t>
+        </is>
+      </c>
+      <c r="C41" s="13">
+        <f>C40/(1+C16/100)^4.25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Terminal value as % of enterprise value</t>
+        </is>
+      </c>
+      <c r="C42" s="16">
+        <f>C41/(C36+C41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>High, as it always is for a cyclical with heavy near-term working capital investment. Treat the DCF as a discipline, not an oracle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>ENTERPRISE VALUE</t>
+        </is>
+      </c>
+      <c r="C43" s="64">
+        <f>C36+C41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="10" t="inlineStr">
+        <is>
           <t>Less: net debt / (add: net cash)</t>
         </is>
       </c>
-      <c r="C41" s="13">
+      <c r="C44" s="13">
         <f>BS!E15-737000</f>
         <v/>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Homebuilding debt $696.9m less cash of $735.9m at 30-Jun-2026: MHO is in a net cash position.</t>
         </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>EQUITY VALUE</t>
-        </is>
-      </c>
-      <c r="C42" s="64">
-        <f>C40-C41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>Shares outstanding (000)</t>
-        </is>
-      </c>
-      <c r="C43" s="13">
-        <f>Assumptions!$C$61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>DCF VALUE PER SHARE</t>
-        </is>
-      </c>
-      <c r="C44" s="8">
-        <f>C42/C43</f>
-        <v/>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
+          <t>EQUITY VALUE</t>
+        </is>
+      </c>
+      <c r="C45" s="64">
+        <f>C43-C44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Shares outstanding (000)</t>
+        </is>
+      </c>
+      <c r="C46" s="13">
+        <f>Assumptions!$C$63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>DCF VALUE PER SHARE</t>
+        </is>
+      </c>
+      <c r="C47" s="8">
+        <f>C45/C46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="6" t="inlineStr">
+        <is>
           <t>Upside / (downside) to current price</t>
         </is>
       </c>
-      <c r="C45" s="65">
-        <f>C44/Assumptions!$C$60-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="6" customHeight="1"/>
-    <row r="47" ht="15.5" customHeight="1">
-      <c r="B47" s="3" t="inlineStr">
+      <c r="C48" s="65">
+        <f>C47/Assumptions!$C$62-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="6" customHeight="1"/>
+    <row r="50" ht="15.5" customHeight="1">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>SENSITIVITY — DCF value per share:  WACC (down) x terminal growth (across)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="3" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="24" t="inlineStr">
+      <c r="C50" s="3" t="n"/>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="n"/>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="3" t="n"/>
+      <c r="J50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="24" t="inlineStr">
         <is>
           <t>WACC  \  terminal growth</t>
         </is>
       </c>
-      <c r="C48" s="66" t="n">
+      <c r="C51" s="66" t="n">
         <v>0.015</v>
       </c>
-      <c r="D48" s="66" t="n">
+      <c r="D51" s="66" t="n">
         <v>0.02</v>
       </c>
-      <c r="E48" s="66" t="n">
+      <c r="E51" s="66" t="n">
         <v>0.025</v>
       </c>
-      <c r="F48" s="66" t="n">
+      <c r="F51" s="66" t="n">
         <v>0.03</v>
       </c>
-      <c r="G48" s="66" t="n">
+      <c r="G51" s="66" t="n">
         <v>0.035</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="67">
-        <f>$C$16+-1.0</f>
-        <v/>
-      </c>
-      <c r="C49" s="68">
-        <f>(F$29*F$30/(1+$B$49/100)^F$31+G$29*G$30/(1+$B$49/100)^G$31+H$29*H$30/(1+$B$49/100)^H$31+I$29*I$30/(1+$B$49/100)^I$31+J$29*J$30/(1+$B$49/100)^J$31+J$29*(1+C$48)/($B$49/100-C$48)/(1+$B$49/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="D49" s="68">
-        <f>(F$29*F$30/(1+$B$49/100)^F$31+G$29*G$30/(1+$B$49/100)^G$31+H$29*H$30/(1+$B$49/100)^H$31+I$29*I$30/(1+$B$49/100)^I$31+J$29*J$30/(1+$B$49/100)^J$31+J$29*(1+D$48)/($B$49/100-D$48)/(1+$B$49/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="E49" s="68">
-        <f>(F$29*F$30/(1+$B$49/100)^F$31+G$29*G$30/(1+$B$49/100)^G$31+H$29*H$30/(1+$B$49/100)^H$31+I$29*I$30/(1+$B$49/100)^I$31+J$29*J$30/(1+$B$49/100)^J$31+J$29*(1+E$48)/($B$49/100-E$48)/(1+$B$49/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="F49" s="68">
-        <f>(F$29*F$30/(1+$B$49/100)^F$31+G$29*G$30/(1+$B$49/100)^G$31+H$29*H$30/(1+$B$49/100)^H$31+I$29*I$30/(1+$B$49/100)^I$31+J$29*J$30/(1+$B$49/100)^J$31+J$29*(1+F$48)/($B$49/100-F$48)/(1+$B$49/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="G49" s="68">
-        <f>(F$29*F$30/(1+$B$49/100)^F$31+G$29*G$30/(1+$B$49/100)^G$31+H$29*H$30/(1+$B$49/100)^H$31+I$29*I$30/(1+$B$49/100)^I$31+J$29*J$30/(1+$B$49/100)^J$31+J$29*(1+G$48)/($B$49/100-G$48)/(1+$B$49/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="67">
-        <f>$C$16+-0.5</f>
-        <v/>
-      </c>
-      <c r="C50" s="68">
-        <f>(F$29*F$30/(1+$B$50/100)^F$31+G$29*G$30/(1+$B$50/100)^G$31+H$29*H$30/(1+$B$50/100)^H$31+I$29*I$30/(1+$B$50/100)^I$31+J$29*J$30/(1+$B$50/100)^J$31+J$29*(1+C$48)/($B$50/100-C$48)/(1+$B$50/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="D50" s="68">
-        <f>(F$29*F$30/(1+$B$50/100)^F$31+G$29*G$30/(1+$B$50/100)^G$31+H$29*H$30/(1+$B$50/100)^H$31+I$29*I$30/(1+$B$50/100)^I$31+J$29*J$30/(1+$B$50/100)^J$31+J$29*(1+D$48)/($B$50/100-D$48)/(1+$B$50/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="E50" s="68">
-        <f>(F$29*F$30/(1+$B$50/100)^F$31+G$29*G$30/(1+$B$50/100)^G$31+H$29*H$30/(1+$B$50/100)^H$31+I$29*I$30/(1+$B$50/100)^I$31+J$29*J$30/(1+$B$50/100)^J$31+J$29*(1+E$48)/($B$50/100-E$48)/(1+$B$50/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="F50" s="68">
-        <f>(F$29*F$30/(1+$B$50/100)^F$31+G$29*G$30/(1+$B$50/100)^G$31+H$29*H$30/(1+$B$50/100)^H$31+I$29*I$30/(1+$B$50/100)^I$31+J$29*J$30/(1+$B$50/100)^J$31+J$29*(1+F$48)/($B$50/100-F$48)/(1+$B$50/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="G50" s="68">
-        <f>(F$29*F$30/(1+$B$50/100)^F$31+G$29*G$30/(1+$B$50/100)^G$31+H$29*H$30/(1+$B$50/100)^H$31+I$29*I$30/(1+$B$50/100)^I$31+J$29*J$30/(1+$B$50/100)^J$31+J$29*(1+G$48)/($B$50/100-G$48)/(1+$B$50/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="67">
-        <f>$C$16+0.0</f>
-        <v/>
-      </c>
-      <c r="C51" s="68">
-        <f>(F$29*F$30/(1+$B$51/100)^F$31+G$29*G$30/(1+$B$51/100)^G$31+H$29*H$30/(1+$B$51/100)^H$31+I$29*I$30/(1+$B$51/100)^I$31+J$29*J$30/(1+$B$51/100)^J$31+J$29*(1+C$48)/($B$51/100-C$48)/(1+$B$51/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="D51" s="68">
-        <f>(F$29*F$30/(1+$B$51/100)^F$31+G$29*G$30/(1+$B$51/100)^G$31+H$29*H$30/(1+$B$51/100)^H$31+I$29*I$30/(1+$B$51/100)^I$31+J$29*J$30/(1+$B$51/100)^J$31+J$29*(1+D$48)/($B$51/100-D$48)/(1+$B$51/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="E51" s="69">
-        <f>(F$29*F$30/(1+$B$51/100)^F$31+G$29*G$30/(1+$B$51/100)^G$31+H$29*H$30/(1+$B$51/100)^H$31+I$29*I$30/(1+$B$51/100)^I$31+J$29*J$30/(1+$B$51/100)^J$31+J$29*(1+E$48)/($B$51/100-E$48)/(1+$B$51/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="F51" s="68">
-        <f>(F$29*F$30/(1+$B$51/100)^F$31+G$29*G$30/(1+$B$51/100)^G$31+H$29*H$30/(1+$B$51/100)^H$31+I$29*I$30/(1+$B$51/100)^I$31+J$29*J$30/(1+$B$51/100)^J$31+J$29*(1+F$48)/($B$51/100-F$48)/(1+$B$51/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="G51" s="68">
-        <f>(F$29*F$30/(1+$B$51/100)^F$31+G$29*G$30/(1+$B$51/100)^G$31+H$29*H$30/(1+$B$51/100)^H$31+I$29*I$30/(1+$B$51/100)^I$31+J$29*J$30/(1+$B$51/100)^J$31+J$29*(1+G$48)/($B$51/100-G$48)/(1+$B$51/100)^4.25-$C$41)/$C$43</f>
-        <v/>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="67">
-        <f>$C$16+0.5</f>
+        <f>$C$16+-1.0</f>
         <v/>
       </c>
       <c r="C52" s="68">
-        <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+J$29*(1+C$48)/($B$52/100-C$48)/(1+$B$52/100)^4.25-$C$41)/$C$43</f>
+        <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+(J$29+(-J$28)+J$28*C$51/$C$37)*(1+C$51)/($B$52/100-C$51)/(1+$B$52/100)^4.25-$C$44)/$C$46</f>
         <v/>
       </c>
       <c r="D52" s="68">
-        <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+J$29*(1+D$48)/($B$52/100-D$48)/(1+$B$52/100)^4.25-$C$41)/$C$43</f>
+        <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+(J$29+(-J$28)+J$28*D$51/$C$37)*(1+D$51)/($B$52/100-D$51)/(1+$B$52/100)^4.25-$C$44)/$C$46</f>
         <v/>
       </c>
       <c r="E52" s="68">
-        <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+J$29*(1+E$48)/($B$52/100-E$48)/(1+$B$52/100)^4.25-$C$41)/$C$43</f>
+        <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+(J$29+(-J$28)+J$28*E$51/$C$37)*(1+E$51)/($B$52/100-E$51)/(1+$B$52/100)^4.25-$C$44)/$C$46</f>
         <v/>
       </c>
       <c r="F52" s="68">
-        <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+J$29*(1+F$48)/($B$52/100-F$48)/(1+$B$52/100)^4.25-$C$41)/$C$43</f>
+        <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+(J$29+(-J$28)+J$28*F$51/$C$37)*(1+F$51)/($B$52/100-F$51)/(1+$B$52/100)^4.25-$C$44)/$C$46</f>
         <v/>
       </c>
       <c r="G52" s="68">
-        <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+J$29*(1+G$48)/($B$52/100-G$48)/(1+$B$52/100)^4.25-$C$41)/$C$43</f>
+        <f>(F$29*F$30/(1+$B$52/100)^F$31+G$29*G$30/(1+$B$52/100)^G$31+H$29*H$30/(1+$B$52/100)^H$31+I$29*I$30/(1+$B$52/100)^I$31+J$29*J$30/(1+$B$52/100)^J$31+(J$29+(-J$28)+J$28*G$51/$C$37)*(1+G$51)/($B$52/100-G$51)/(1+$B$52/100)^4.25-$C$44)/$C$46</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="67">
+        <f>$C$16+-0.5</f>
+        <v/>
+      </c>
+      <c r="C53" s="68">
+        <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+(J$29+(-J$28)+J$28*C$51/$C$37)*(1+C$51)/($B$53/100-C$51)/(1+$B$53/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="D53" s="68">
+        <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+(J$29+(-J$28)+J$28*D$51/$C$37)*(1+D$51)/($B$53/100-D$51)/(1+$B$53/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="E53" s="68">
+        <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+(J$29+(-J$28)+J$28*E$51/$C$37)*(1+E$51)/($B$53/100-E$51)/(1+$B$53/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="F53" s="68">
+        <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+(J$29+(-J$28)+J$28*F$51/$C$37)*(1+F$51)/($B$53/100-F$51)/(1+$B$53/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="G53" s="68">
+        <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+(J$29+(-J$28)+J$28*G$51/$C$37)*(1+G$51)/($B$53/100-G$51)/(1+$B$53/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="67">
+        <f>$C$16+0.0</f>
+        <v/>
+      </c>
+      <c r="C54" s="68">
+        <f>(F$29*F$30/(1+$B$54/100)^F$31+G$29*G$30/(1+$B$54/100)^G$31+H$29*H$30/(1+$B$54/100)^H$31+I$29*I$30/(1+$B$54/100)^I$31+J$29*J$30/(1+$B$54/100)^J$31+(J$29+(-J$28)+J$28*C$51/$C$37)*(1+C$51)/($B$54/100-C$51)/(1+$B$54/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="D54" s="68">
+        <f>(F$29*F$30/(1+$B$54/100)^F$31+G$29*G$30/(1+$B$54/100)^G$31+H$29*H$30/(1+$B$54/100)^H$31+I$29*I$30/(1+$B$54/100)^I$31+J$29*J$30/(1+$B$54/100)^J$31+(J$29+(-J$28)+J$28*D$51/$C$37)*(1+D$51)/($B$54/100-D$51)/(1+$B$54/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="E54" s="69">
+        <f>(F$29*F$30/(1+$B$54/100)^F$31+G$29*G$30/(1+$B$54/100)^G$31+H$29*H$30/(1+$B$54/100)^H$31+I$29*I$30/(1+$B$54/100)^I$31+J$29*J$30/(1+$B$54/100)^J$31+(J$29+(-J$28)+J$28*E$51/$C$37)*(1+E$51)/($B$54/100-E$51)/(1+$B$54/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="F54" s="68">
+        <f>(F$29*F$30/(1+$B$54/100)^F$31+G$29*G$30/(1+$B$54/100)^G$31+H$29*H$30/(1+$B$54/100)^H$31+I$29*I$30/(1+$B$54/100)^I$31+J$29*J$30/(1+$B$54/100)^J$31+(J$29+(-J$28)+J$28*F$51/$C$37)*(1+F$51)/($B$54/100-F$51)/(1+$B$54/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="G54" s="68">
+        <f>(F$29*F$30/(1+$B$54/100)^F$31+G$29*G$30/(1+$B$54/100)^G$31+H$29*H$30/(1+$B$54/100)^H$31+I$29*I$30/(1+$B$54/100)^I$31+J$29*J$30/(1+$B$54/100)^J$31+(J$29+(-J$28)+J$28*G$51/$C$37)*(1+G$51)/($B$54/100-G$51)/(1+$B$54/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="67">
+        <f>$C$16+0.5</f>
+        <v/>
+      </c>
+      <c r="C55" s="68">
+        <f>(F$29*F$30/(1+$B$55/100)^F$31+G$29*G$30/(1+$B$55/100)^G$31+H$29*H$30/(1+$B$55/100)^H$31+I$29*I$30/(1+$B$55/100)^I$31+J$29*J$30/(1+$B$55/100)^J$31+(J$29+(-J$28)+J$28*C$51/$C$37)*(1+C$51)/($B$55/100-C$51)/(1+$B$55/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="D55" s="68">
+        <f>(F$29*F$30/(1+$B$55/100)^F$31+G$29*G$30/(1+$B$55/100)^G$31+H$29*H$30/(1+$B$55/100)^H$31+I$29*I$30/(1+$B$55/100)^I$31+J$29*J$30/(1+$B$55/100)^J$31+(J$29+(-J$28)+J$28*D$51/$C$37)*(1+D$51)/($B$55/100-D$51)/(1+$B$55/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="E55" s="68">
+        <f>(F$29*F$30/(1+$B$55/100)^F$31+G$29*G$30/(1+$B$55/100)^G$31+H$29*H$30/(1+$B$55/100)^H$31+I$29*I$30/(1+$B$55/100)^I$31+J$29*J$30/(1+$B$55/100)^J$31+(J$29+(-J$28)+J$28*E$51/$C$37)*(1+E$51)/($B$55/100-E$51)/(1+$B$55/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="F55" s="68">
+        <f>(F$29*F$30/(1+$B$55/100)^F$31+G$29*G$30/(1+$B$55/100)^G$31+H$29*H$30/(1+$B$55/100)^H$31+I$29*I$30/(1+$B$55/100)^I$31+J$29*J$30/(1+$B$55/100)^J$31+(J$29+(-J$28)+J$28*F$51/$C$37)*(1+F$51)/($B$55/100-F$51)/(1+$B$55/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="G55" s="68">
+        <f>(F$29*F$30/(1+$B$55/100)^F$31+G$29*G$30/(1+$B$55/100)^G$31+H$29*H$30/(1+$B$55/100)^H$31+I$29*I$30/(1+$B$55/100)^I$31+J$29*J$30/(1+$B$55/100)^J$31+(J$29+(-J$28)+J$28*G$51/$C$37)*(1+G$51)/($B$55/100-G$51)/(1+$B$55/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="67">
         <f>$C$16+1.0</f>
         <v/>
       </c>
-      <c r="C53" s="68">
-        <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+J$29*(1+C$48)/($B$53/100-C$48)/(1+$B$53/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="D53" s="68">
-        <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+J$29*(1+D$48)/($B$53/100-D$48)/(1+$B$53/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="E53" s="68">
-        <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+J$29*(1+E$48)/($B$53/100-E$48)/(1+$B$53/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="F53" s="68">
-        <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+J$29*(1+F$48)/($B$53/100-F$48)/(1+$B$53/100)^4.25-$C$41)/$C$43</f>
-        <v/>
-      </c>
-      <c r="G53" s="68">
-        <f>(F$29*F$30/(1+$B$53/100)^F$31+G$29*G$30/(1+$B$53/100)^G$31+H$29*H$30/(1+$B$53/100)^H$31+I$29*I$30/(1+$B$53/100)^I$31+J$29*J$30/(1+$B$53/100)^J$31+J$29*(1+G$48)/($B$53/100-G$48)/(1+$B$53/100)^4.25-$C$41)/$C$43</f>
+      <c r="C56" s="68">
+        <f>(F$29*F$30/(1+$B$56/100)^F$31+G$29*G$30/(1+$B$56/100)^G$31+H$29*H$30/(1+$B$56/100)^H$31+I$29*I$30/(1+$B$56/100)^I$31+J$29*J$30/(1+$B$56/100)^J$31+(J$29+(-J$28)+J$28*C$51/$C$37)*(1+C$51)/($B$56/100-C$51)/(1+$B$56/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="D56" s="68">
+        <f>(F$29*F$30/(1+$B$56/100)^F$31+G$29*G$30/(1+$B$56/100)^G$31+H$29*H$30/(1+$B$56/100)^H$31+I$29*I$30/(1+$B$56/100)^I$31+J$29*J$30/(1+$B$56/100)^J$31+(J$29+(-J$28)+J$28*D$51/$C$37)*(1+D$51)/($B$56/100-D$51)/(1+$B$56/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="E56" s="68">
+        <f>(F$29*F$30/(1+$B$56/100)^F$31+G$29*G$30/(1+$B$56/100)^G$31+H$29*H$30/(1+$B$56/100)^H$31+I$29*I$30/(1+$B$56/100)^I$31+J$29*J$30/(1+$B$56/100)^J$31+(J$29+(-J$28)+J$28*E$51/$C$37)*(1+E$51)/($B$56/100-E$51)/(1+$B$56/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="F56" s="68">
+        <f>(F$29*F$30/(1+$B$56/100)^F$31+G$29*G$30/(1+$B$56/100)^G$31+H$29*H$30/(1+$B$56/100)^H$31+I$29*I$30/(1+$B$56/100)^I$31+J$29*J$30/(1+$B$56/100)^J$31+(J$29+(-J$28)+J$28*F$51/$C$37)*(1+F$51)/($B$56/100-F$51)/(1+$B$56/100)^4.25-$C$44)/$C$46</f>
+        <v/>
+      </c>
+      <c r="G56" s="68">
+        <f>(F$29*F$30/(1+$B$56/100)^F$31+G$29*G$30/(1+$B$56/100)^G$31+H$29*H$30/(1+$B$56/100)^H$31+I$29*I$30/(1+$B$56/100)^I$31+J$29*J$30/(1+$B$56/100)^J$31+(J$29+(-J$28)+J$28*G$51/$C$37)*(1+G$51)/($B$56/100-G$51)/(1+$B$56/100)^4.25-$C$44)/$C$46</f>
         <v/>
       </c>
     </row>
